--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\UNIVERSIDAD ECONOMÍA\Tercer Año\Proyecto-evolucion-salarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{3898E4BC-C720-4145-9E62-DA38D54DA32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evolución PBG MZA" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId18" roundtripDataChecksum="/dUSXa82hxQOGMb+5WJan/aJb6jPiaBSIQkW1CqgTQI="/>
     </ext>
@@ -103,11 +114,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="167" formatCode="0.000E+00_)"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0"/>
-    <numFmt numFmtId="169" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="170" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="171" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.000E+00_)"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -216,36 +227,36 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
@@ -255,7 +266,7 @@
     <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -480,9 +491,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -499,7 +510,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1970</v>
       </c>
@@ -516,7 +527,7 @@
         <v>4.7536083333333332E-10</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1971</v>
       </c>
@@ -534,7 +545,7 @@
         <v>6.4042000000000005E-10</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1972</v>
       </c>
@@ -552,7 +563,7 @@
         <v>1.0147766666666666E-9</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1973</v>
       </c>
@@ -583,7 +594,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1974</v>
       </c>
@@ -601,7 +612,7 @@
         <v>2.0206541666666667E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1975</v>
       </c>
@@ -629,7 +640,7 @@
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1976</v>
       </c>
@@ -647,7 +658,7 @@
         <v>3.1086300000000001E-8</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1977</v>
       </c>
@@ -665,7 +676,7 @@
         <v>8.5808049999999979E-8</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1978</v>
       </c>
@@ -683,7 +694,7 @@
         <v>2.3640874999999998E-7</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1979</v>
       </c>
@@ -701,7 +712,7 @@
         <v>6.1350683333333345E-7</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1980</v>
       </c>
@@ -719,7 +730,7 @@
         <v>1.2317019999999998E-6</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1981</v>
       </c>
@@ -737,7 +748,7 @@
         <v>2.5185499999999998E-6</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1982</v>
       </c>
@@ -755,7 +766,7 @@
         <v>6.6685833333333333E-6</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>1983</v>
       </c>
@@ -773,7 +784,7 @@
         <v>2.9595141666666666E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>1984</v>
       </c>
@@ -791,7 +802,7 @@
         <v>2.1507783333333334E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>1985</v>
       </c>
@@ -809,7 +820,7 @@
         <v>1.6607925000000001E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>1986</v>
       </c>
@@ -827,7 +838,7 @@
         <v>3.1570041666666667E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1987</v>
       </c>
@@ -845,7 +856,7 @@
         <v>7.3032416666666657E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>1988</v>
       </c>
@@ -863,7 +874,7 @@
         <v>3.2350000000000004E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>1989</v>
       </c>
@@ -881,7 +892,7 @@
         <v>1.0285535833333335</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>1990</v>
       </c>
@@ -899,7 +910,7 @@
         <v>24.828900000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>1991</v>
       </c>
@@ -920,7 +931,7 @@
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>1992</v>
       </c>
@@ -939,7 +950,7 @@
       </c>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>1993</v>
       </c>
@@ -958,7 +969,7 @@
       </c>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>1994</v>
       </c>
@@ -994,7 +1005,7 @@
       <c r="V26" s="17"/>
       <c r="W26" s="17"/>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>1995</v>
       </c>
@@ -1012,7 +1023,7 @@
         <v>100.35939999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>1996</v>
       </c>
@@ -1030,7 +1041,7 @@
         <v>100.51560000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>1997</v>
       </c>
@@ -1048,7 +1059,7 @@
         <v>101.04689999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>1998</v>
       </c>
@@ -1066,7 +1077,7 @@
         <v>101.9813</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>1999</v>
       </c>
@@ -1084,7 +1095,7 @@
         <v>100.7915</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>2000</v>
       </c>
@@ -1102,7 +1113,7 @@
         <v>99.844899999999996</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>2001</v>
       </c>
@@ -1120,7 +1131,7 @@
         <v>98.781666666666652</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>2002</v>
       </c>
@@ -1138,7 +1149,7 @@
         <v>124.33499999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>2003</v>
       </c>
@@ -1156,7 +1167,7 @@
         <v>141.05000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>2004</v>
       </c>
@@ -1174,7 +1185,7 @@
         <v>147.28</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A37" s="3">
         <v>2005</v>
       </c>
@@ -1192,7 +1203,7 @@
         <v>167.48</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A38" s="3">
         <v>2006</v>
       </c>
@@ -1210,7 +1221,7 @@
         <v>179.08</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A39" s="3">
         <v>2007</v>
       </c>
@@ -1228,7 +1239,7 @@
         <v>194.89</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A40" s="3">
         <v>2008</v>
       </c>
@@ -1246,7 +1257,7 @@
         <v>211.61661758333335</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A41" s="3">
         <v>2009</v>
       </c>
@@ -1264,7 +1275,7 @@
         <v>224.88780650000001</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A42" s="3">
         <v>2010</v>
       </c>
@@ -1282,7 +1293,7 @@
         <v>248.41401550000003</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A43" s="3">
         <v>2011</v>
       </c>
@@ -1300,7 +1311,7 @@
         <v>272.69744600000001</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A44" s="3">
         <v>2012</v>
       </c>
@@ -1347,7 +1358,7 @@
         <v>14178694.442281883</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A45" s="3">
         <v>2013</v>
       </c>
@@ -1365,7 +1376,7 @@
         <v>331.95090075000002</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A46" s="3">
         <v>2014</v>
       </c>
@@ -1381,7 +1392,7 @@
       </c>
       <c r="E46" s="4"/>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
         <v>2015</v>
       </c>
@@ -1398,7 +1409,7 @@
       <c r="E47" s="4"/>
       <c r="O47" s="17"/>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A48" s="3">
         <v>2016</v>
       </c>
@@ -1415,7 +1426,7 @@
       <c r="E48" s="4"/>
       <c r="O48" s="17"/>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A49" s="3">
         <v>2017</v>
       </c>
@@ -1432,7 +1443,7 @@
       <c r="E49" s="4"/>
       <c r="O49" s="17"/>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A50" s="3">
         <v>2018</v>
       </c>
@@ -1449,7 +1460,7 @@
       <c r="E50" s="4"/>
       <c r="O50" s="17"/>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A51" s="3">
         <v>2019</v>
       </c>
@@ -1466,7 +1477,7 @@
       <c r="E51" s="4"/>
       <c r="O51" s="17"/>
     </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A52" s="3">
         <v>2020</v>
       </c>
@@ -1483,7 +1494,7 @@
       <c r="E52" s="4"/>
       <c r="O52" s="17"/>
     </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A53" s="3">
         <v>2021</v>
       </c>
@@ -1500,7 +1511,7 @@
       <c r="E53" s="4"/>
       <c r="O53" s="17"/>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A54" s="3">
         <v>2022</v>
       </c>
@@ -1517,37 +1528,37 @@
       <c r="E54" s="4"/>
       <c r="O54" s="17"/>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O55" s="17"/>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O56" s="17"/>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O57" s="17"/>
     </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O58" s="17"/>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O59" s="17"/>
     </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O60" s="17"/>
     </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O61" s="17"/>
     </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O62" s="17"/>
     </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O63" s="17"/>
     </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O64" s="17"/>
     </row>
-    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="15:15" ht="14.4" x14ac:dyDescent="0.3">
       <c r="O65" s="17"/>
     </row>
   </sheetData>

--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3898E4BC-C720-4145-9E62-DA38D54DA32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{3898E4BC-C720-4145-9E62-DA38D54DA32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6084B5FD-6B53-484D-A069-9512CFC7B59F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -217,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -270,6 +270,9 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -493,7 +496,7 @@
   <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -506,7 +509,8 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="20"/>
+      <c r="G1" s="20" t="s">
         <v>4</v>
       </c>
     </row>
@@ -523,7 +527,8 @@
       <c r="D2" s="4">
         <v>100</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="5"/>
+      <c r="G2" s="5">
         <v>4.7536083333333332E-10</v>
       </c>
     </row>
@@ -541,7 +546,8 @@
         <f t="shared" ref="D3:D17" si="0">(B3/$B$2)*100</f>
         <v>106.69367960948219</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="5"/>
+      <c r="G3" s="5">
         <v>6.4042000000000005E-10</v>
       </c>
     </row>
@@ -559,7 +565,8 @@
         <f t="shared" si="0"/>
         <v>113.66493315891906</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="5"/>
+      <c r="G4" s="5">
         <v>1.0147766666666666E-9</v>
       </c>
     </row>
@@ -577,11 +584,11 @@
         <f t="shared" si="0"/>
         <v>116.23967073987811</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="5"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="5">
         <v>1.6267208333333335E-9</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
@@ -608,7 +615,8 @@
         <f t="shared" si="0"/>
         <v>129.65255399929811</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="5"/>
+      <c r="G6" s="5">
         <v>2.0206541666666667E-9</v>
       </c>
     </row>
@@ -626,11 +634,11 @@
         <f t="shared" si="0"/>
         <v>113.32673962288229</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="5"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="5">
         <v>5.7142666666666667E-9</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
       <c r="J7" s="10"/>
@@ -654,7 +662,8 @@
         <f t="shared" si="0"/>
         <v>128.91235682608558</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="5"/>
+      <c r="G8" s="5">
         <v>3.1086300000000001E-8</v>
       </c>
     </row>
@@ -672,7 +681,8 @@
         <f t="shared" si="0"/>
         <v>121.44019398270747</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="5"/>
+      <c r="G9" s="5">
         <v>8.5808049999999979E-8</v>
       </c>
     </row>
@@ -690,7 +700,8 @@
         <f t="shared" si="0"/>
         <v>135.14979421242384</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="5"/>
+      <c r="G10" s="5">
         <v>2.3640874999999998E-7</v>
       </c>
     </row>
@@ -708,7 +719,8 @@
         <f t="shared" si="0"/>
         <v>153.47924576460454</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="5"/>
+      <c r="G11" s="5">
         <v>6.1350683333333345E-7</v>
       </c>
     </row>
@@ -726,7 +738,8 @@
         <f t="shared" si="0"/>
         <v>136.94923906454392</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="5"/>
+      <c r="G12" s="5">
         <v>1.2317019999999998E-6</v>
       </c>
     </row>
@@ -744,7 +757,8 @@
         <f t="shared" si="0"/>
         <v>112.25153941868997</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="5"/>
+      <c r="G13" s="5">
         <v>2.5185499999999998E-6</v>
       </c>
     </row>
@@ -762,7 +776,8 @@
         <f t="shared" si="0"/>
         <v>114.99537376766742</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="5"/>
+      <c r="G14" s="5">
         <v>6.6685833333333333E-6</v>
       </c>
     </row>
@@ -780,7 +795,8 @@
         <f t="shared" si="0"/>
         <v>133.7651150177073</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="5"/>
+      <c r="G15" s="5">
         <v>2.9595141666666666E-5</v>
       </c>
     </row>
@@ -798,7 +814,8 @@
         <f t="shared" si="0"/>
         <v>129.03678652330663</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="5"/>
+      <c r="G16" s="5">
         <v>2.1507783333333334E-4</v>
       </c>
     </row>
@@ -816,7 +833,8 @@
         <f t="shared" si="0"/>
         <v>122.71001499537377</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="5"/>
+      <c r="G17" s="5">
         <v>1.6607925000000001E-3</v>
       </c>
     </row>
@@ -834,7 +852,8 @@
         <f>D17</f>
         <v>122.71001499537377</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="5"/>
+      <c r="G18" s="5">
         <v>3.1570041666666667E-3</v>
       </c>
     </row>
@@ -852,7 +871,8 @@
         <f t="shared" ref="D19:D22" si="1">$D$17*(B19/$B$18)</f>
         <v>124.28891506339684</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="5"/>
+      <c r="G19" s="5">
         <v>7.3032416666666657E-3</v>
       </c>
     </row>
@@ -870,7 +890,8 @@
         <f t="shared" si="1"/>
         <v>121.27216266089812</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="13"/>
+      <c r="G20" s="13">
         <v>3.2350000000000004E-2</v>
       </c>
     </row>
@@ -888,7 +909,8 @@
         <f t="shared" si="1"/>
         <v>116.19930480577673</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="13"/>
+      <c r="G21" s="13">
         <v>1.0285535833333335</v>
       </c>
     </row>
@@ -906,7 +928,8 @@
         <f t="shared" si="1"/>
         <v>116.29880857099063</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="14"/>
+      <c r="G22" s="14">
         <v>24.828900000000001</v>
       </c>
     </row>
@@ -924,11 +947,11 @@
         <f>D22</f>
         <v>116.29880857099063</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="14"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="14">
         <v>67.453100000000006</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -945,7 +968,8 @@
         <f t="shared" ref="D24:D54" si="2">$D$22*(B24/$B$23)</f>
         <v>126.15283596275975</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="14"/>
+      <c r="G24" s="14">
         <v>84.248900000000006</v>
       </c>
       <c r="H24" s="10"/>
@@ -964,7 +988,8 @@
         <f t="shared" si="2"/>
         <v>139.18020081296368</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="14"/>
+      <c r="G25" s="14">
         <v>93.188999999999993</v>
       </c>
       <c r="H25" s="10"/>
@@ -983,11 +1008,11 @@
         <f t="shared" si="2"/>
         <v>145.21471521057683</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="14"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="14">
         <v>97.081800000000001</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="17"/>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
       <c r="J26" s="17"/>
@@ -1019,7 +1044,8 @@
         <f t="shared" si="2"/>
         <v>141.82165694844821</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="14"/>
+      <c r="G27" s="14">
         <v>100.35939999999999</v>
       </c>
     </row>
@@ -1037,7 +1063,8 @@
         <f t="shared" si="2"/>
         <v>145.88418474583582</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="14"/>
+      <c r="G28" s="14">
         <v>100.51560000000001</v>
       </c>
     </row>
@@ -1055,7 +1082,8 @@
         <f t="shared" si="2"/>
         <v>159.70262326453033</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="14"/>
+      <c r="G29" s="14">
         <v>101.04689999999999</v>
       </c>
     </row>
@@ -1073,7 +1101,8 @@
         <f t="shared" si="2"/>
         <v>170.14514382981497</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="14"/>
+      <c r="G30" s="14">
         <v>101.9813</v>
       </c>
     </row>
@@ -1091,7 +1120,8 @@
         <f t="shared" si="2"/>
         <v>165.91889102418298</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="14"/>
+      <c r="G31" s="14">
         <v>100.7915</v>
       </c>
     </row>
@@ -1109,7 +1139,8 @@
         <f t="shared" si="2"/>
         <v>161.42552234834085</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="14"/>
+      <c r="G32" s="14">
         <v>99.844899999999996</v>
       </c>
     </row>
@@ -1127,7 +1158,8 @@
         <f t="shared" si="2"/>
         <v>149.24881513943413</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="18"/>
+      <c r="G33" s="18">
         <v>98.781666666666652</v>
       </c>
     </row>
@@ -1145,7 +1177,8 @@
         <f t="shared" si="2"/>
         <v>139.37189172111891</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="18"/>
+      <c r="G34" s="18">
         <v>124.33499999999999</v>
       </c>
     </row>
@@ -1163,7 +1196,8 @@
         <f t="shared" si="2"/>
         <v>167.48462269348113</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="18"/>
+      <c r="G35" s="18">
         <v>141.05000000000001</v>
       </c>
     </row>
@@ -1181,7 +1215,8 @@
         <f t="shared" si="2"/>
         <v>195.01039897657333</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="18"/>
+      <c r="G36" s="18">
         <v>147.28</v>
       </c>
     </row>
@@ -1199,7 +1234,8 @@
         <f t="shared" si="2"/>
         <v>204.08107433612355</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="18"/>
+      <c r="G37" s="18">
         <v>167.48</v>
       </c>
     </row>
@@ -1217,7 +1253,8 @@
         <f t="shared" si="2"/>
         <v>219.83515831455196</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="18"/>
+      <c r="G38" s="18">
         <v>179.08</v>
       </c>
     </row>
@@ -1235,7 +1272,8 @@
         <f t="shared" si="2"/>
         <v>229.00590069370071</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="18"/>
+      <c r="G39" s="18">
         <v>194.89</v>
       </c>
     </row>
@@ -1253,8 +1291,9 @@
         <f t="shared" si="2"/>
         <v>234.28610581772668</v>
       </c>
-      <c r="E40" s="18">
-        <v>211.61661758333335</v>
+      <c r="E40" s="18"/>
+      <c r="G40" s="18">
+        <v>238.54535999999999</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
@@ -1271,8 +1310,9 @@
         <f t="shared" si="2"/>
         <v>227.75142607223748</v>
       </c>
-      <c r="E41" s="18">
-        <v>224.88780650000001</v>
+      <c r="E41" s="18"/>
+      <c r="G41" s="18">
+        <v>287.92424951999999</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
@@ -1289,8 +1329,9 @@
         <f t="shared" si="2"/>
         <v>237.82335302435985</v>
       </c>
-      <c r="E42" s="18">
-        <v>248.41401550000003</v>
+      <c r="E42" s="18"/>
+      <c r="G42" s="18">
+        <v>334.56797794223996</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
@@ -1307,8 +1348,9 @@
         <f t="shared" si="2"/>
         <v>246.37969369127993</v>
       </c>
-      <c r="E43" s="18">
-        <v>272.69744600000001</v>
+      <c r="E43" s="18"/>
+      <c r="G43" s="18">
+        <v>427.9124437881249</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
@@ -1325,11 +1367,11 @@
         <f t="shared" si="2"/>
         <v>242.89193346709314</v>
       </c>
-      <c r="E44" s="18">
-        <v>300.08478674999998</v>
-      </c>
+      <c r="E44" s="18"/>
       <c r="F44" s="16"/>
-      <c r="G44" s="17"/>
+      <c r="G44" s="18">
+        <v>527.61604319075809</v>
+      </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
       <c r="J44" s="17"/>
@@ -1372,8 +1414,9 @@
         <f t="shared" si="2"/>
         <v>254.8423917486889</v>
       </c>
-      <c r="E45" s="18">
-        <v>331.95090075000002</v>
+      <c r="E45" s="18"/>
+      <c r="G45" s="18">
+        <v>650.55058125420476</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
@@ -1391,6 +1434,9 @@
         <v>245.4533277328573</v>
       </c>
       <c r="E46" s="4"/>
+      <c r="G46" s="4">
+        <v>844.4146544679578</v>
+      </c>
     </row>
     <row r="47" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
       <c r="A47" s="3">
@@ -1407,6 +1453,9 @@
         <v>254.44768913833843</v>
       </c>
       <c r="E47" s="4"/>
+      <c r="G47" s="4">
+        <v>1192.3134921087565</v>
+      </c>
       <c r="O47" s="17"/>
     </row>
     <row r="48" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
@@ -1424,6 +1473,9 @@
         <v>239.80612475273261</v>
       </c>
       <c r="E48" s="4"/>
+      <c r="G48" s="4">
+        <v>1513.0458214860121</v>
+      </c>
       <c r="O48" s="17"/>
     </row>
     <row r="49" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
@@ -1441,6 +1493,9 @@
         <v>244.87175954715681</v>
       </c>
       <c r="E49" s="4"/>
+      <c r="G49" s="4">
+        <v>2066.8205921498925</v>
+      </c>
       <c r="O49" s="17"/>
     </row>
     <row r="50" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
@@ -1458,6 +1513,9 @@
         <v>243.61857426234812</v>
       </c>
       <c r="E50" s="4"/>
+      <c r="G50" s="4">
+        <v>2546.3229695286677</v>
+      </c>
       <c r="O50" s="17"/>
     </row>
     <row r="51" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
@@ -1475,6 +1533,9 @@
         <v>240.48483146394625</v>
       </c>
       <c r="E51" s="4"/>
+      <c r="G51" s="4">
+        <v>3860.2256218054604</v>
+      </c>
       <c r="O51" s="17"/>
     </row>
     <row r="52" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
@@ -1492,6 +1553,9 @@
         <v>221.32965430741552</v>
       </c>
       <c r="E52" s="4"/>
+      <c r="G52" s="4">
+        <v>5921.5861038495759</v>
+      </c>
       <c r="O52" s="17"/>
     </row>
     <row r="53" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
@@ -1509,6 +1573,9 @@
         <v>244.52020483896297</v>
       </c>
       <c r="E53" s="4"/>
+      <c r="G53" s="4">
+        <v>8136.2593066893178</v>
+      </c>
       <c r="O53" s="17"/>
     </row>
     <row r="54" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
@@ -1526,6 +1593,7 @@
         <v>254.25387471241018</v>
       </c>
       <c r="E54" s="4"/>
+      <c r="G54" s="4"/>
       <c r="O54" s="17"/>
     </row>
     <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">

--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{3898E4BC-C720-4145-9E62-DA38D54DA32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6084B5FD-6B53-484D-A069-9512CFC7B59F}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{3898E4BC-C720-4145-9E62-DA38D54DA32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4268E232-17E2-4EB2-8100-2691A27CFD01}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/971a82d91f2470ed/Escritorio/ECONOMIA/3 AÑO/Lab Ciencia de Datos/Proyecto historia economica/Proyecto-evolucion-salarios/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{3898E4BC-C720-4145-9E62-DA38D54DA32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4268E232-17E2-4EB2-8100-2691A27CFD01}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F8EBC8-26D0-4E4C-B80A-03199622A859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evolución PBG MZA" sheetId="14" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId18" roundtripDataChecksum="/dUSXa82hxQOGMb+5WJan/aJb6jPiaBSIQkW1CqgTQI="/>
     </ext>
@@ -83,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="10">
   <si>
     <t>Año</t>
   </si>
@@ -108,17 +97,23 @@
   <si>
     <t>Miles de pesos de 1993</t>
   </si>
+  <si>
+    <t>Tasa de conversion 1 peso=0,0001 austral</t>
+  </si>
+  <si>
+    <t>PBG convertido</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="0.000E+00_)"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="167" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="165" formatCode="0.000E+00_)"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -176,7 +171,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -213,11 +208,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -227,7 +233,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -248,13 +254,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -266,15 +272,15 @@
     <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,9 +500,12 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:X65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="14.42578125" style="22"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="46.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -509,12 +518,17 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="20"/>
-      <c r="G1" s="20" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F1" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1970</v>
       </c>
@@ -527,12 +541,18 @@
       <c r="D2" s="4">
         <v>100</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="G2" s="5">
+      <c r="E2" s="5">
         <v>4.7536083333333332E-10</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F2">
+        <v>1E-4</v>
+      </c>
+      <c r="G2" s="22">
+        <f>B2/$F$2</f>
+        <v>3134300</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>1971</v>
       </c>
@@ -546,12 +566,15 @@
         <f t="shared" ref="D3:D17" si="0">(B3/$B$2)*100</f>
         <v>106.69367960948219</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="G3" s="5">
+      <c r="E3" s="5">
         <v>6.4042000000000005E-10</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G3" s="22">
+        <f>B3/$F$2</f>
+        <v>3344100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>1972</v>
       </c>
@@ -565,12 +588,15 @@
         <f t="shared" si="0"/>
         <v>113.66493315891906</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="G4" s="5">
+      <c r="E4" s="5">
         <v>1.0147766666666666E-9</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="22">
+        <f t="shared" ref="G4:G17" si="1">B4/$F$2</f>
+        <v>3562599.9999999995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>1973</v>
       </c>
@@ -584,10 +610,13 @@
         <f t="shared" si="0"/>
         <v>116.23967073987811</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5">
+        <v>1.6267208333333335E-9</v>
+      </c>
       <c r="F5" s="8"/>
-      <c r="G5" s="5">
-        <v>1.6267208333333335E-9</v>
+      <c r="G5" s="22">
+        <f t="shared" si="1"/>
+        <v>3643299.9999999995</v>
       </c>
       <c r="H5" s="8"/>
       <c r="I5" s="8"/>
@@ -601,7 +630,7 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
     </row>
-    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1974</v>
       </c>
@@ -615,12 +644,15 @@
         <f t="shared" si="0"/>
         <v>129.65255399929811</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="G6" s="5">
+      <c r="E6" s="5">
         <v>2.0206541666666667E-9</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G6" s="22">
+        <f t="shared" si="1"/>
+        <v>4063700</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>1975</v>
       </c>
@@ -634,10 +666,13 @@
         <f t="shared" si="0"/>
         <v>113.32673962288229</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="5">
+        <v>5.7142666666666667E-9</v>
+      </c>
       <c r="F7" s="10"/>
-      <c r="G7" s="5">
-        <v>5.7142666666666667E-9</v>
+      <c r="G7" s="22">
+        <f t="shared" si="1"/>
+        <v>3551999.9999999995</v>
       </c>
       <c r="H7" s="10"/>
       <c r="I7" s="10"/>
@@ -648,7 +683,7 @@
       <c r="N7" s="10"/>
       <c r="O7" s="10"/>
     </row>
-    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>1976</v>
       </c>
@@ -662,12 +697,15 @@
         <f t="shared" si="0"/>
         <v>128.91235682608558</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="G8" s="5">
+      <c r="E8" s="5">
         <v>3.1086300000000001E-8</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G8" s="22">
+        <f t="shared" si="1"/>
+        <v>4040500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>1977</v>
       </c>
@@ -681,12 +719,15 @@
         <f t="shared" si="0"/>
         <v>121.44019398270747</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="G9" s="5">
+      <c r="E9" s="5">
         <v>8.5808049999999979E-8</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G9" s="22">
+        <f t="shared" si="1"/>
+        <v>3806300</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1978</v>
       </c>
@@ -700,12 +741,15 @@
         <f t="shared" si="0"/>
         <v>135.14979421242384</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="G10" s="5">
+      <c r="E10" s="5">
         <v>2.3640874999999998E-7</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G10" s="22">
+        <f t="shared" si="1"/>
+        <v>4236000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1979</v>
       </c>
@@ -719,12 +763,15 @@
         <f t="shared" si="0"/>
         <v>153.47924576460454</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="G11" s="5">
+      <c r="E11" s="5">
         <v>6.1350683333333345E-7</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G11" s="22">
+        <f t="shared" si="1"/>
+        <v>4810500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1980</v>
       </c>
@@ -738,12 +785,15 @@
         <f t="shared" si="0"/>
         <v>136.94923906454392</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="G12" s="5">
+      <c r="E12" s="5">
         <v>1.2317019999999998E-6</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G12" s="22">
+        <f t="shared" si="1"/>
+        <v>4292400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1981</v>
       </c>
@@ -757,12 +807,15 @@
         <f t="shared" si="0"/>
         <v>112.25153941868997</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="G13" s="5">
+      <c r="E13" s="5">
         <v>2.5185499999999998E-6</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G13" s="22">
+        <f t="shared" si="1"/>
+        <v>3518299.9999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1982</v>
       </c>
@@ -776,12 +829,15 @@
         <f t="shared" si="0"/>
         <v>114.99537376766742</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="G14" s="5">
+      <c r="E14" s="5">
         <v>6.6685833333333333E-6</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="22">
+        <f t="shared" si="1"/>
+        <v>3604300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1983</v>
       </c>
@@ -795,12 +851,15 @@
         <f t="shared" si="0"/>
         <v>133.7651150177073</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="G15" s="5">
+      <c r="E15" s="5">
         <v>2.9595141666666666E-5</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="22">
+        <f t="shared" si="1"/>
+        <v>4192599.9999999995</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1984</v>
       </c>
@@ -814,12 +873,15 @@
         <f t="shared" si="0"/>
         <v>129.03678652330663</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="G16" s="5">
+      <c r="E16" s="5">
         <v>2.1507783333333334E-4</v>
       </c>
-    </row>
-    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G16" s="22">
+        <f t="shared" si="1"/>
+        <v>4044400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1985</v>
       </c>
@@ -833,12 +895,15 @@
         <f t="shared" si="0"/>
         <v>122.71001499537377</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="G17" s="5">
+      <c r="E17" s="5">
         <v>1.6607925000000001E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="22">
+        <f t="shared" si="1"/>
+        <v>3846100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1986</v>
       </c>
@@ -852,12 +917,14 @@
         <f>D17</f>
         <v>122.71001499537377</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="G18" s="5">
+      <c r="E18" s="5">
         <v>3.1570041666666667E-3</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G18" s="12">
+        <v>267608.7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1987</v>
       </c>
@@ -868,15 +935,17 @@
         <v>6</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" ref="D19:D22" si="1">$D$17*(B19/$B$18)</f>
+        <f t="shared" ref="D19:D22" si="2">$D$17*(B19/$B$18)</f>
         <v>124.28891506339684</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="G19" s="5">
+      <c r="E19" s="5">
         <v>7.3032416666666657E-3</v>
       </c>
-    </row>
-    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G19" s="12">
+        <v>271052</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1988</v>
       </c>
@@ -887,15 +956,17 @@
         <v>6</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>121.27216266089812</v>
       </c>
-      <c r="E20" s="13"/>
-      <c r="G20" s="13">
+      <c r="E20" s="13">
         <v>3.2350000000000004E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G20" s="12">
+        <v>264473</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1989</v>
       </c>
@@ -906,15 +977,17 @@
         <v>6</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>116.19930480577673</v>
       </c>
-      <c r="E21" s="13"/>
-      <c r="G21" s="13">
+      <c r="E21" s="13">
         <v>1.0285535833333335</v>
       </c>
-    </row>
-    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G21" s="12">
+        <v>253410</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1990</v>
       </c>
@@ -925,15 +998,17 @@
         <v>6</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>116.29880857099063</v>
       </c>
-      <c r="E22" s="14"/>
-      <c r="G22" s="14">
+      <c r="E22" s="14">
         <v>24.828900000000001</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G22" s="12">
+        <v>253627</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1991</v>
       </c>
@@ -947,14 +1022,16 @@
         <f>D22</f>
         <v>116.29880857099063</v>
       </c>
-      <c r="E23" s="14"/>
+      <c r="E23" s="14">
+        <v>67.453100000000006</v>
+      </c>
       <c r="F23" s="10"/>
-      <c r="G23" s="14">
-        <v>67.453100000000006</v>
+      <c r="G23" s="15">
+        <v>6485506.9469233276</v>
       </c>
       <c r="H23" s="10"/>
     </row>
-    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1992</v>
       </c>
@@ -965,16 +1042,18 @@
         <v>7</v>
       </c>
       <c r="D24" s="4">
-        <f t="shared" ref="D24:D54" si="2">$D$22*(B24/$B$23)</f>
+        <f t="shared" ref="D24:D54" si="3">$D$22*(B24/$B$23)</f>
         <v>126.15283596275975</v>
       </c>
-      <c r="E24" s="14"/>
-      <c r="G24" s="14">
+      <c r="E24" s="14">
         <v>84.248900000000006</v>
       </c>
+      <c r="G24" s="15">
+        <v>7035025.5867938362</v>
+      </c>
       <c r="H24" s="10"/>
     </row>
-    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1993</v>
       </c>
@@ -985,16 +1064,18 @@
         <v>7</v>
       </c>
       <c r="D25" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>139.18020081296368</v>
       </c>
-      <c r="E25" s="14"/>
-      <c r="G25" s="14">
+      <c r="E25" s="14">
         <v>93.188999999999993</v>
       </c>
+      <c r="G25" s="15">
+        <v>7761508.2247009035</v>
+      </c>
       <c r="H25" s="10"/>
     </row>
-    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1994</v>
       </c>
@@ -1005,13 +1086,15 @@
         <v>7</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>145.21471521057683</v>
       </c>
-      <c r="E26" s="14"/>
+      <c r="E26" s="14">
+        <v>97.081800000000001</v>
+      </c>
       <c r="F26" s="16"/>
-      <c r="G26" s="14">
-        <v>97.081800000000001</v>
+      <c r="G26" s="15">
+        <v>8098028.310572112</v>
       </c>
       <c r="H26" s="17"/>
       <c r="I26" s="17"/>
@@ -1030,7 +1113,7 @@
       <c r="V26" s="17"/>
       <c r="W26" s="17"/>
     </row>
-    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1995</v>
       </c>
@@ -1041,15 +1124,17 @@
         <v>7</v>
       </c>
       <c r="D27" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>141.82165694844821</v>
       </c>
-      <c r="E27" s="14"/>
-      <c r="G27" s="14">
+      <c r="E27" s="14">
         <v>100.35939999999999</v>
       </c>
-    </row>
-    <row r="28" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G27" s="15">
+        <v>7908811.3856461942</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1996</v>
       </c>
@@ -1060,15 +1145,17 @@
         <v>7</v>
       </c>
       <c r="D28" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>145.88418474583582</v>
       </c>
-      <c r="E28" s="14"/>
-      <c r="G28" s="14">
+      <c r="E28" s="14">
         <v>100.51560000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G28" s="15">
+        <v>8135361.8772270568</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>1997</v>
       </c>
@@ -1079,15 +1166,17 @@
         <v>7</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>159.70262326453033</v>
       </c>
-      <c r="E29" s="14"/>
-      <c r="G29" s="14">
+      <c r="E29" s="14">
         <v>101.04689999999999</v>
       </c>
-    </row>
-    <row r="30" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G29" s="15">
+        <v>8905959.4449048098</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>1998</v>
       </c>
@@ -1098,15 +1187,17 @@
         <v>7</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>170.14514382981497</v>
       </c>
-      <c r="E30" s="14"/>
-      <c r="G30" s="14">
+      <c r="E30" s="14">
         <v>101.9813</v>
       </c>
-    </row>
-    <row r="31" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G30" s="15">
+        <v>9488295.9322833791</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>1999</v>
       </c>
@@ -1117,15 +1208,17 @@
         <v>7</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>165.91889102418298</v>
       </c>
-      <c r="E31" s="14"/>
-      <c r="G31" s="14">
+      <c r="E31" s="14">
         <v>100.7915</v>
       </c>
-    </row>
-    <row r="32" spans="1:23" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G31" s="15">
+        <v>9252615.1693661101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2000</v>
       </c>
@@ -1136,15 +1229,17 @@
         <v>7</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>161.42552234834085</v>
       </c>
-      <c r="E32" s="14"/>
-      <c r="G32" s="14">
+      <c r="E32" s="14">
         <v>99.844899999999996</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G32" s="15">
+        <v>9002038.4513383135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2001</v>
       </c>
@@ -1155,15 +1250,17 @@
         <v>7</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>149.24881513943413</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="G33" s="18">
+      <c r="E33" s="18">
         <v>98.781666666666652</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G33" s="15">
+        <v>8322993.4966704417</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2002</v>
       </c>
@@ -1174,15 +1271,17 @@
         <v>7</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>139.37189172111891</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="G34" s="18">
+      <c r="E34" s="18">
         <v>124.33499999999999</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G34" s="15">
+        <v>7772198.0394271128</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2003</v>
       </c>
@@ -1193,15 +1292,17 @@
         <v>7</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>167.48462269348113</v>
       </c>
-      <c r="E35" s="18"/>
-      <c r="G35" s="18">
+      <c r="E35" s="18">
         <v>141.05000000000001</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G35" s="15">
+        <v>9339929.5945354141</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2004</v>
       </c>
@@ -1212,15 +1313,17 @@
         <v>7</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>195.01039897657333</v>
       </c>
-      <c r="E36" s="18"/>
-      <c r="G36" s="18">
+      <c r="E36" s="18">
         <v>147.28</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G36" s="19">
+        <v>10874929.097083896</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2005</v>
       </c>
@@ -1231,15 +1334,17 @@
         <v>7</v>
       </c>
       <c r="D37" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>204.08107433612355</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="G37" s="18">
+      <c r="E37" s="18">
         <v>167.48</v>
       </c>
-    </row>
-    <row r="38" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G37" s="19">
+        <v>11380763.411127962</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2006</v>
       </c>
@@ -1250,15 +1355,17 @@
         <v>7</v>
       </c>
       <c r="D38" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>219.83515831455196</v>
       </c>
-      <c r="E38" s="18"/>
-      <c r="G38" s="18">
+      <c r="E38" s="18">
         <v>179.08</v>
       </c>
-    </row>
-    <row r="39" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G38" s="19">
+        <v>12259303.976933869</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2007</v>
       </c>
@@ -1269,15 +1376,17 @@
         <v>7</v>
       </c>
       <c r="D39" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>229.00590069370071</v>
       </c>
-      <c r="E39" s="18"/>
-      <c r="G39" s="18">
+      <c r="E39" s="18">
         <v>194.89</v>
       </c>
-    </row>
-    <row r="40" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G39" s="19">
+        <v>12770718.617713338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2008</v>
       </c>
@@ -1288,15 +1397,17 @@
         <v>7</v>
       </c>
       <c r="D40" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>234.28610581772668</v>
       </c>
-      <c r="E40" s="18"/>
-      <c r="G40" s="18">
-        <v>238.54535999999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="E40" s="18">
+        <v>211.61661758333335</v>
+      </c>
+      <c r="G40" s="19">
+        <v>13065173.97313641</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2009</v>
       </c>
@@ -1307,15 +1418,17 @@
         <v>7</v>
       </c>
       <c r="D41" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>227.75142607223748</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="G41" s="18">
-        <v>287.92424951999999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="E41" s="18">
+        <v>224.88780650000001</v>
+      </c>
+      <c r="G41" s="19">
+        <v>12700761.719855074</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2010</v>
       </c>
@@ -1326,15 +1439,17 @@
         <v>7</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>237.82335302435985</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="G42" s="18">
-        <v>334.56797794223996</v>
-      </c>
-    </row>
-    <row r="43" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="E42" s="18">
+        <v>248.41401550000003</v>
+      </c>
+      <c r="G42" s="19">
+        <v>13262431.723353179</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2011</v>
       </c>
@@ -1345,15 +1460,17 @@
         <v>7</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>246.37969369127993</v>
       </c>
-      <c r="E43" s="18"/>
-      <c r="G43" s="18">
-        <v>427.9124437881249</v>
-      </c>
-    </row>
-    <row r="44" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="E43" s="18">
+        <v>272.69744600000001</v>
+      </c>
+      <c r="G43" s="19">
+        <v>13739583.703819767</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2012</v>
       </c>
@@ -1364,13 +1481,15 @@
         <v>7</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>242.89193346709314</v>
       </c>
-      <c r="E44" s="18"/>
+      <c r="E44" s="18">
+        <v>300.08478674999998</v>
+      </c>
       <c r="F44" s="16"/>
-      <c r="G44" s="18">
-        <v>527.61604319075809</v>
+      <c r="G44" s="19">
+        <v>13545085.639384663</v>
       </c>
       <c r="H44" s="17"/>
       <c r="I44" s="17"/>
@@ -1400,7 +1519,7 @@
         <v>14178694.442281883</v>
       </c>
     </row>
-    <row r="45" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2013</v>
       </c>
@@ -1411,15 +1530,17 @@
         <v>7</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>254.8423917486889</v>
       </c>
-      <c r="E45" s="18"/>
-      <c r="G45" s="18">
-        <v>650.55058125420476</v>
-      </c>
-    </row>
-    <row r="46" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="E45" s="18">
+        <v>331.95090075000002</v>
+      </c>
+      <c r="G45" s="19">
+        <v>14211513.62051825</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2014</v>
       </c>
@@ -1430,15 +1551,15 @@
         <v>7</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>245.4533277328573</v>
       </c>
       <c r="E46" s="4"/>
-      <c r="G46" s="4">
-        <v>844.4146544679578</v>
-      </c>
-    </row>
-    <row r="47" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="G46" s="19">
+        <v>13687924.078647634</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2015</v>
       </c>
@@ -1449,16 +1570,16 @@
         <v>7</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>254.44768913833843</v>
       </c>
       <c r="E47" s="4"/>
-      <c r="G47" s="4">
-        <v>1192.3134921087565</v>
+      <c r="G47" s="19">
+        <v>14189502.676873595</v>
       </c>
       <c r="O47" s="17"/>
     </row>
-    <row r="48" spans="1:24" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2016</v>
       </c>
@@ -1469,16 +1590,16 @@
         <v>7</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>239.80612475273261</v>
       </c>
       <c r="E48" s="4"/>
-      <c r="G48" s="4">
-        <v>1513.0458214860121</v>
+      <c r="G48" s="19">
+        <v>13373002.759948755</v>
       </c>
       <c r="O48" s="17"/>
     </row>
-    <row r="49" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2017</v>
       </c>
@@ -1489,16 +1610,16 @@
         <v>7</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>244.87175954715681</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="G49" s="4">
-        <v>2066.8205921498925</v>
+      <c r="G49" s="19">
+        <v>13655492.409271004</v>
       </c>
       <c r="O49" s="17"/>
     </row>
-    <row r="50" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2018</v>
       </c>
@@ -1509,16 +1630,16 @@
         <v>7</v>
       </c>
       <c r="D50" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>243.61857426234812</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="G50" s="4">
-        <v>2546.3229695286677</v>
+      <c r="G50" s="19">
+        <v>13585607.412423011</v>
       </c>
       <c r="O50" s="17"/>
     </row>
-    <row r="51" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2019</v>
       </c>
@@ -1529,16 +1650,16 @@
         <v>7</v>
       </c>
       <c r="D51" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>240.48483146394625</v>
       </c>
       <c r="E51" s="4"/>
-      <c r="G51" s="4">
-        <v>3860.2256218054604</v>
+      <c r="G51" s="19">
+        <v>13410851.44597216</v>
       </c>
       <c r="O51" s="17"/>
     </row>
-    <row r="52" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2020</v>
       </c>
@@ -1549,16 +1670,16 @@
         <v>7</v>
       </c>
       <c r="D52" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>221.32965430741552</v>
       </c>
       <c r="E52" s="4"/>
-      <c r="G52" s="4">
-        <v>5921.5861038495759</v>
+      <c r="G52" s="19">
+        <v>12342645.880973661</v>
       </c>
       <c r="O52" s="17"/>
     </row>
-    <row r="53" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2021</v>
       </c>
@@ -1569,16 +1690,16 @@
         <v>7</v>
       </c>
       <c r="D53" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>244.52020483896297</v>
       </c>
       <c r="E53" s="4"/>
-      <c r="G53" s="4">
-        <v>8136.2593066893178</v>
+      <c r="G53" s="19">
+        <v>13635887.646933109</v>
       </c>
       <c r="O53" s="17"/>
     </row>
-    <row r="54" spans="1:15" ht="28.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2022</v>
       </c>
@@ -1589,44 +1710,46 @@
         <v>7</v>
       </c>
       <c r="D54" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>254.25387471241018</v>
       </c>
       <c r="E54" s="4"/>
-      <c r="G54" s="4"/>
+      <c r="G54" s="19">
+        <v>14178694.442281883</v>
+      </c>
       <c r="O54" s="17"/>
     </row>
-    <row r="55" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O55" s="17"/>
     </row>
-    <row r="56" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O56" s="17"/>
     </row>
-    <row r="57" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O57" s="17"/>
     </row>
-    <row r="58" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O58" s="17"/>
     </row>
-    <row r="59" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O59" s="17"/>
     </row>
-    <row r="60" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O60" s="17"/>
     </row>
-    <row r="61" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O61" s="17"/>
     </row>
-    <row r="62" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O62" s="17"/>
     </row>
-    <row r="63" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O63" s="17"/>
     </row>
-    <row r="64" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="O64" s="17"/>
     </row>
-    <row r="65" spans="15:15" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="65" spans="15:15" x14ac:dyDescent="0.25">
       <c r="O65" s="17"/>
     </row>
   </sheetData>

--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\UNIVERSIDAD ECONOMÍA\Tercer Año\Proyecto-evolucion-salarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F8EBC8-26D0-4E4C-B80A-03199622A859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746A2DB8-8A79-4E13-8BD3-92D6F4161408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evolución PBG MZA" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId18" roundtripDataChecksum="/dUSXa82hxQOGMb+5WJan/aJb6jPiaBSIQkW1CqgTQI="/>
@@ -115,7 +115,7 @@
     <numFmt numFmtId="167" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -155,6 +155,12 @@
       <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -223,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -278,9 +284,15 @@
     <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,6 +826,15 @@
         <f t="shared" si="1"/>
         <v>3518299.9999999995</v>
       </c>
+      <c r="I13" s="23">
+        <v>6485507</v>
+      </c>
+      <c r="J13" s="23">
+        <v>7035026</v>
+      </c>
+      <c r="K13" s="23">
+        <v>7761508</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
@@ -836,6 +857,18 @@
         <f t="shared" si="1"/>
         <v>3604300</v>
       </c>
+      <c r="I14">
+        <f>I13/I15</f>
+        <v>24.984713709506547</v>
+      </c>
+      <c r="J14">
+        <f t="shared" ref="J14:K14" si="2">J13/J15</f>
+        <v>25.354277414774263</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="2"/>
+        <v>26.13610358123011</v>
+      </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
@@ -858,6 +891,15 @@
         <f t="shared" si="1"/>
         <v>4192599.9999999995</v>
       </c>
+      <c r="I15" s="24">
+        <v>259579</v>
+      </c>
+      <c r="J15" s="24">
+        <v>277469</v>
+      </c>
+      <c r="K15" s="24">
+        <v>296965</v>
+      </c>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
@@ -902,6 +944,10 @@
         <f t="shared" si="1"/>
         <v>3846100</v>
       </c>
+      <c r="I17">
+        <f>AVERAGE(I14:K14)</f>
+        <v>25.491698235170304</v>
+      </c>
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
@@ -923,6 +969,10 @@
       <c r="G18" s="12">
         <v>267608.7</v>
       </c>
+      <c r="H18">
+        <f>G18*$I$17</f>
+        <v>6821800.22550622</v>
+      </c>
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
@@ -935,7 +985,7 @@
         <v>6</v>
       </c>
       <c r="D19" s="4">
-        <f t="shared" ref="D19:D22" si="2">$D$17*(B19/$B$18)</f>
+        <f t="shared" ref="D19:D22" si="3">$D$17*(B19/$B$18)</f>
         <v>124.28891506339684</v>
       </c>
       <c r="E19" s="5">
@@ -943,6 +993,10 @@
       </c>
       <c r="G19" s="12">
         <v>271052</v>
+      </c>
+      <c r="H19">
+        <f t="shared" ref="H19:H22" si="4">G19*$I$17</f>
+        <v>6909575.790039381</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -956,7 +1010,7 @@
         <v>6</v>
       </c>
       <c r="D20" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>121.27216266089812</v>
       </c>
       <c r="E20" s="13">
@@ -964,6 +1018,10 @@
       </c>
       <c r="G20" s="12">
         <v>264473</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="4"/>
+        <v>6741865.9073501956</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -977,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="D21" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>116.19930480577673</v>
       </c>
       <c r="E21" s="13">
@@ -985,6 +1043,10 @@
       </c>
       <c r="G21" s="12">
         <v>253410</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="4"/>
+        <v>6459851.2497745063</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -998,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="4">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>116.29880857099063</v>
       </c>
       <c r="E22" s="14">
@@ -1006,6 +1068,10 @@
       </c>
       <c r="G22" s="12">
         <v>253627</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="4"/>
+        <v>6465382.9482915383</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1042,7 +1108,7 @@
         <v>7</v>
       </c>
       <c r="D24" s="4">
-        <f t="shared" ref="D24:D54" si="3">$D$22*(B24/$B$23)</f>
+        <f t="shared" ref="D24:D54" si="5">$D$22*(B24/$B$23)</f>
         <v>126.15283596275975</v>
       </c>
       <c r="E24" s="14">
@@ -1064,7 +1130,7 @@
         <v>7</v>
       </c>
       <c r="D25" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>139.18020081296368</v>
       </c>
       <c r="E25" s="14">
@@ -1086,7 +1152,7 @@
         <v>7</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>145.21471521057683</v>
       </c>
       <c r="E26" s="14">
@@ -1124,7 +1190,7 @@
         <v>7</v>
       </c>
       <c r="D27" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>141.82165694844821</v>
       </c>
       <c r="E27" s="14">
@@ -1145,7 +1211,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>145.88418474583582</v>
       </c>
       <c r="E28" s="14">
@@ -1166,7 +1232,7 @@
         <v>7</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>159.70262326453033</v>
       </c>
       <c r="E29" s="14">
@@ -1187,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>170.14514382981497</v>
       </c>
       <c r="E30" s="14">
@@ -1208,7 +1274,7 @@
         <v>7</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>165.91889102418298</v>
       </c>
       <c r="E31" s="14">
@@ -1229,7 +1295,7 @@
         <v>7</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>161.42552234834085</v>
       </c>
       <c r="E32" s="14">
@@ -1250,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>149.24881513943413</v>
       </c>
       <c r="E33" s="18">
@@ -1271,7 +1337,7 @@
         <v>7</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>139.37189172111891</v>
       </c>
       <c r="E34" s="18">
@@ -1292,7 +1358,7 @@
         <v>7</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>167.48462269348113</v>
       </c>
       <c r="E35" s="18">
@@ -1313,7 +1379,7 @@
         <v>7</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>195.01039897657333</v>
       </c>
       <c r="E36" s="18">
@@ -1334,7 +1400,7 @@
         <v>7</v>
       </c>
       <c r="D37" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>204.08107433612355</v>
       </c>
       <c r="E37" s="18">
@@ -1355,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="D38" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>219.83515831455196</v>
       </c>
       <c r="E38" s="18">
@@ -1376,7 +1442,7 @@
         <v>7</v>
       </c>
       <c r="D39" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>229.00590069370071</v>
       </c>
       <c r="E39" s="18">
@@ -1397,7 +1463,7 @@
         <v>7</v>
       </c>
       <c r="D40" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>234.28610581772668</v>
       </c>
       <c r="E40" s="18">
@@ -1418,7 +1484,7 @@
         <v>7</v>
       </c>
       <c r="D41" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>227.75142607223748</v>
       </c>
       <c r="E41" s="18">
@@ -1439,7 +1505,7 @@
         <v>7</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>237.82335302435985</v>
       </c>
       <c r="E42" s="18">
@@ -1460,7 +1526,7 @@
         <v>7</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>246.37969369127993</v>
       </c>
       <c r="E43" s="18">
@@ -1481,7 +1547,7 @@
         <v>7</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>242.89193346709314</v>
       </c>
       <c r="E44" s="18">
@@ -1530,7 +1596,7 @@
         <v>7</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>254.8423917486889</v>
       </c>
       <c r="E45" s="18">
@@ -1551,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>245.4533277328573</v>
       </c>
       <c r="E46" s="4"/>
@@ -1570,7 +1636,7 @@
         <v>7</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>254.44768913833843</v>
       </c>
       <c r="E47" s="4"/>
@@ -1590,7 +1656,7 @@
         <v>7</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>239.80612475273261</v>
       </c>
       <c r="E48" s="4"/>
@@ -1610,7 +1676,7 @@
         <v>7</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>244.87175954715681</v>
       </c>
       <c r="E49" s="4"/>
@@ -1630,7 +1696,7 @@
         <v>7</v>
       </c>
       <c r="D50" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>243.61857426234812</v>
       </c>
       <c r="E50" s="4"/>
@@ -1650,7 +1716,7 @@
         <v>7</v>
       </c>
       <c r="D51" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>240.48483146394625</v>
       </c>
       <c r="E51" s="4"/>
@@ -1670,7 +1736,7 @@
         <v>7</v>
       </c>
       <c r="D52" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>221.32965430741552</v>
       </c>
       <c r="E52" s="4"/>
@@ -1690,7 +1756,7 @@
         <v>7</v>
       </c>
       <c r="D53" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>244.52020483896297</v>
       </c>
       <c r="E53" s="4"/>
@@ -1710,7 +1776,7 @@
         <v>7</v>
       </c>
       <c r="D54" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>254.25387471241018</v>
       </c>
       <c r="E54" s="4"/>

--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\UNIVERSIDAD ECONOMÍA\Tercer Año\Proyecto-evolucion-salarios\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{746A2DB8-8A79-4E13-8BD3-92D6F4161408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C025D463-802B-4327-AD1A-CD0D5F2B98EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evolución PBG MZA" sheetId="14" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId18" roundtripDataChecksum="/dUSXa82hxQOGMb+5WJan/aJb6jPiaBSIQkW1CqgTQI="/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="12">
   <si>
     <t>Año</t>
   </si>
@@ -103,19 +103,27 @@
   <si>
     <t>PBG convertido</t>
   </si>
+  <si>
+    <t>Prueba de como poner la variación entre cambios de monedas</t>
+  </si>
+  <si>
+    <t>PBI a precios de mercadoBase Ferreres (mill. de $ 1993)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="0.000E+00_)"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="_(* #,##0.00000_);_(* \(#,##0.00000\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="168" formatCode="_(* #,##0.0000_);_(* \(#,##0.0000\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="169" formatCode="#,##0\ \ \ \ "/>
+    <numFmt numFmtId="170" formatCode="#,##0\ \ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -162,6 +170,29 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="62"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -177,7 +208,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -225,11 +256,116 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="169" fontId="8" fillId="0" borderId="14"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -287,15 +423,55 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal_PBI pk por Sectores final" xfId="1" xr:uid="{01AEF0FB-32A3-424C-9468-ECB2E56EA492}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -539,6 +715,12 @@
       <c r="G1" s="21" t="s">
         <v>9</v>
       </c>
+      <c r="M1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
@@ -563,6 +745,12 @@
         <f>B2/$F$2</f>
         <v>3134300</v>
       </c>
+      <c r="M2" s="42">
+        <v>1969</v>
+      </c>
+      <c r="N2" s="41">
+        <v>152643.77335610622</v>
+      </c>
     </row>
     <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
@@ -585,6 +773,12 @@
         <f>B3/$F$2</f>
         <v>3344100</v>
       </c>
+      <c r="M3" s="43">
+        <v>1970</v>
+      </c>
+      <c r="N3" s="41">
+        <v>160860.95636173122</v>
+      </c>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
@@ -606,6 +800,12 @@
       <c r="G4" s="22">
         <f t="shared" ref="G4:G17" si="1">B4/$F$2</f>
         <v>3562599.9999999995</v>
+      </c>
+      <c r="M4" s="42">
+        <v>1971</v>
+      </c>
+      <c r="N4" s="41">
+        <v>166912.60622155317</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -635,8 +835,12 @@
       <c r="J5" s="8"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
+      <c r="M5" s="42">
+        <v>1972</v>
+      </c>
+      <c r="N5" s="41">
+        <v>170379.33445085437</v>
+      </c>
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
       <c r="Q5" s="9"/>
@@ -662,6 +866,12 @@
       <c r="G6" s="22">
         <f t="shared" si="1"/>
         <v>4063700</v>
+      </c>
+      <c r="M6" s="42">
+        <v>1973</v>
+      </c>
+      <c r="N6" s="41">
+        <v>176760.97430606186</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -691,8 +901,12 @@
       <c r="J7" s="10"/>
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
+      <c r="M7" s="42">
+        <v>1974</v>
+      </c>
+      <c r="N7" s="41">
+        <v>186316.01795022786</v>
+      </c>
       <c r="O7" s="10"/>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -716,6 +930,12 @@
         <f t="shared" si="1"/>
         <v>4040500</v>
       </c>
+      <c r="M8" s="42">
+        <v>1975</v>
+      </c>
+      <c r="N8" s="41">
+        <v>185210.55146568603</v>
+      </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
@@ -738,6 +958,12 @@
         <f t="shared" si="1"/>
         <v>3806300</v>
       </c>
+      <c r="M9" s="42">
+        <v>1976</v>
+      </c>
+      <c r="N9" s="41">
+        <v>185188.55213266029</v>
+      </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
@@ -760,6 +986,16 @@
         <f t="shared" si="1"/>
         <v>4236000</v>
       </c>
+      <c r="I10" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="40"/>
+      <c r="M10" s="42">
+        <v>1977</v>
+      </c>
+      <c r="N10" s="41">
+        <v>197015.02691173065</v>
+      </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
@@ -778,9 +1014,19 @@
       <c r="E11" s="5">
         <v>6.1350683333333345E-7</v>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="23">
         <f t="shared" si="1"/>
         <v>4810500</v>
+      </c>
+      <c r="H11" s="26"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="27"/>
+      <c r="K11" s="28"/>
+      <c r="M11" s="42">
+        <v>1978</v>
+      </c>
+      <c r="N11" s="41">
+        <v>190666.38605606163</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -800,9 +1046,19 @@
       <c r="E12" s="5">
         <v>1.2317019999999998E-6</v>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="23">
         <f t="shared" si="1"/>
         <v>4292400</v>
+      </c>
+      <c r="H12" s="29"/>
+      <c r="I12" s="30"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="M12" s="42">
+        <v>1979</v>
+      </c>
+      <c r="N12" s="41">
+        <v>203891.65176001663</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -822,18 +1078,25 @@
       <c r="E13" s="5">
         <v>2.5185499999999998E-6</v>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="23">
         <f t="shared" si="1"/>
         <v>3518299.9999999995</v>
       </c>
-      <c r="I13" s="23">
+      <c r="H13" s="29"/>
+      <c r="I13" s="32">
         <v>6485507</v>
       </c>
-      <c r="J13" s="23">
+      <c r="J13" s="32">
         <v>7035026</v>
       </c>
-      <c r="K13" s="23">
+      <c r="K13" s="33">
         <v>7761508</v>
+      </c>
+      <c r="M13" s="43">
+        <v>1980</v>
+      </c>
+      <c r="N13" s="41">
+        <v>207011.43217472488</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -853,21 +1116,28 @@
       <c r="E14" s="5">
         <v>6.6685833333333333E-6</v>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="23">
         <f t="shared" si="1"/>
         <v>3604300</v>
       </c>
-      <c r="I14">
+      <c r="H14" s="29"/>
+      <c r="I14" s="30">
         <f>I13/I15</f>
         <v>24.984713709506547</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="30">
         <f t="shared" ref="J14:K14" si="2">J13/J15</f>
         <v>25.354277414774263</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="31">
         <f t="shared" si="2"/>
         <v>26.13610358123011</v>
+      </c>
+      <c r="M14" s="42">
+        <v>1981</v>
+      </c>
+      <c r="N14" s="41">
+        <v>195787.08557126726</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -887,18 +1157,25 @@
       <c r="E15" s="5">
         <v>2.9595141666666666E-5</v>
       </c>
-      <c r="G15" s="22">
+      <c r="G15" s="23">
         <f t="shared" si="1"/>
         <v>4192599.9999999995</v>
       </c>
-      <c r="I15" s="24">
+      <c r="H15" s="29"/>
+      <c r="I15" s="34">
         <v>259579</v>
       </c>
-      <c r="J15" s="24">
+      <c r="J15" s="34">
         <v>277469</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="35">
         <v>296965</v>
+      </c>
+      <c r="M15" s="42">
+        <v>1982</v>
+      </c>
+      <c r="N15" s="41">
+        <v>189602.24152446413</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -918,9 +1195,19 @@
       <c r="E16" s="5">
         <v>2.1507783333333334E-4</v>
       </c>
-      <c r="G16" s="22">
+      <c r="G16" s="23">
         <f t="shared" si="1"/>
         <v>4044400</v>
+      </c>
+      <c r="H16" s="29"/>
+      <c r="I16" s="30"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="M16" s="42">
+        <v>1983</v>
+      </c>
+      <c r="N16" s="41">
+        <v>197400.61051265232</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -940,13 +1227,22 @@
       <c r="E17" s="5">
         <v>1.6607925000000001E-3</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="23">
         <f t="shared" si="1"/>
         <v>3846100</v>
       </c>
-      <c r="I17">
+      <c r="H17" s="29"/>
+      <c r="I17" s="30">
         <f>AVERAGE(I14:K14)</f>
         <v>25.491698235170304</v>
+      </c>
+      <c r="J17" s="30"/>
+      <c r="K17" s="31"/>
+      <c r="M17" s="42">
+        <v>1984</v>
+      </c>
+      <c r="N17" s="41">
+        <v>201349.02459711238</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -966,12 +1262,21 @@
       <c r="E18" s="5">
         <v>3.1570041666666667E-3</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="24">
         <v>267608.7</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="29">
         <f>G18*$I$17</f>
         <v>6821800.22550622</v>
+      </c>
+      <c r="I18" s="30"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
+      <c r="M18" s="42">
+        <v>1985</v>
+      </c>
+      <c r="N18" s="41">
+        <v>187351.74596487361</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -991,12 +1296,21 @@
       <c r="E19" s="5">
         <v>7.3032416666666657E-3</v>
       </c>
-      <c r="G19" s="12">
+      <c r="G19" s="24">
         <v>271052</v>
       </c>
-      <c r="H19">
+      <c r="H19" s="29">
         <f t="shared" ref="H19:H22" si="4">G19*$I$17</f>
         <v>6909575.790039381</v>
+      </c>
+      <c r="I19" s="30"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="31"/>
+      <c r="M19" s="42">
+        <v>1986</v>
+      </c>
+      <c r="N19" s="41">
+        <v>200726.11957615431</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1016,12 +1330,21 @@
       <c r="E20" s="13">
         <v>3.2350000000000004E-2</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="24">
         <v>264473</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="29">
         <f t="shared" si="4"/>
         <v>6741865.9073501956</v>
+      </c>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="31"/>
+      <c r="M20" s="42">
+        <v>1987</v>
+      </c>
+      <c r="N20" s="41">
+        <v>205926.37181563661</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1041,12 +1364,21 @@
       <c r="E21" s="13">
         <v>1.0285535833333335</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="24">
         <v>253410</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="29">
         <f t="shared" si="4"/>
         <v>6459851.2497745063</v>
+      </c>
+      <c r="I21" s="30"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="31"/>
+      <c r="M21" s="42">
+        <v>1988</v>
+      </c>
+      <c r="N21" s="41">
+        <v>202022.16389395422</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1066,12 +1398,21 @@
       <c r="E22" s="14">
         <v>24.828900000000001</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="24">
         <v>253627</v>
       </c>
-      <c r="H22">
+      <c r="H22" s="29">
         <f t="shared" si="4"/>
         <v>6465382.9482915383</v>
+      </c>
+      <c r="I22" s="30"/>
+      <c r="J22" s="30"/>
+      <c r="K22" s="31"/>
+      <c r="M22" s="42">
+        <v>1989</v>
+      </c>
+      <c r="N22" s="41">
+        <v>188010.819664468</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1092,10 +1433,19 @@
         <v>67.453100000000006</v>
       </c>
       <c r="F23" s="10"/>
-      <c r="G23" s="15">
+      <c r="G23" s="25">
         <v>6485506.9469233276</v>
       </c>
-      <c r="H23" s="10"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="31"/>
+      <c r="M23" s="43">
+        <v>1990</v>
+      </c>
+      <c r="N23" s="41">
+        <v>184568.76708091571</v>
+      </c>
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
@@ -1114,10 +1464,19 @@
       <c r="E24" s="14">
         <v>84.248900000000006</v>
       </c>
-      <c r="G24" s="15">
+      <c r="G24" s="25">
         <v>7035025.5867938362</v>
       </c>
-      <c r="H24" s="10"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="31"/>
+      <c r="M24" s="42">
+        <v>1991</v>
+      </c>
+      <c r="N24" s="41">
+        <v>204093.82543139864</v>
+      </c>
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
@@ -1136,10 +1495,19 @@
       <c r="E25" s="14">
         <v>93.188999999999993</v>
       </c>
-      <c r="G25" s="15">
+      <c r="G25" s="25">
         <v>7761508.2247009035</v>
       </c>
-      <c r="H25" s="10"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="39"/>
+      <c r="M25" s="42">
+        <v>1992</v>
+      </c>
+      <c r="N25" s="41">
+        <v>223701.26799433088</v>
+      </c>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
@@ -1167,8 +1535,12 @@
       <c r="J26" s="17"/>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="17"/>
+      <c r="M26" s="42">
+        <v>1993</v>
+      </c>
+      <c r="N26" s="41">
+        <v>236504.9802315725</v>
+      </c>
       <c r="O26" s="17"/>
       <c r="P26" s="17"/>
       <c r="Q26" s="17"/>
@@ -1199,6 +1571,12 @@
       <c r="G27" s="15">
         <v>7908811.3856461942</v>
       </c>
+      <c r="M27" s="42">
+        <v>1994</v>
+      </c>
+      <c r="N27" s="41">
+        <v>250307.88553631518</v>
+      </c>
     </row>
     <row r="28" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
@@ -1220,6 +1598,12 @@
       <c r="G28" s="15">
         <v>8135361.8772270568</v>
       </c>
+      <c r="M28" s="42">
+        <v>1995</v>
+      </c>
+      <c r="N28" s="41">
+        <v>243186.10151946038</v>
+      </c>
     </row>
     <row r="29" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
@@ -1241,6 +1625,12 @@
       <c r="G29" s="15">
         <v>8905959.4449048098</v>
       </c>
+      <c r="M29" s="42">
+        <v>1996</v>
+      </c>
+      <c r="N29" s="41">
+        <v>256626.24305584718</v>
+      </c>
     </row>
     <row r="30" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
@@ -1262,6 +1652,12 @@
       <c r="G30" s="15">
         <v>9488295.9322833791</v>
       </c>
+      <c r="M30" s="42">
+        <v>1997</v>
+      </c>
+      <c r="N30" s="41">
+        <v>277441.31762238021</v>
+      </c>
     </row>
     <row r="31" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
@@ -1283,6 +1679,12 @@
       <c r="G31" s="15">
         <v>9252615.1693661101</v>
       </c>
+      <c r="M31" s="42">
+        <v>1998</v>
+      </c>
+      <c r="N31" s="41">
+        <v>288122.8046077239</v>
+      </c>
     </row>
     <row r="32" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
@@ -1304,6 +1706,12 @@
       <c r="G32" s="15">
         <v>9002038.4513383135</v>
       </c>
+      <c r="M32" s="42">
+        <v>1999</v>
+      </c>
+      <c r="N32" s="41">
+        <v>278369.01387171785</v>
+      </c>
     </row>
     <row r="33" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
@@ -1325,6 +1733,12 @@
       <c r="G33" s="15">
         <v>8322993.4966704417</v>
       </c>
+      <c r="M33" s="43">
+        <v>2000</v>
+      </c>
+      <c r="N33" s="41">
+        <v>276172.18535265006</v>
+      </c>
     </row>
     <row r="34" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
@@ -1346,6 +1760,12 @@
       <c r="G34" s="15">
         <v>7772198.0394271128</v>
       </c>
+      <c r="M34" s="42">
+        <v>2001</v>
+      </c>
+      <c r="N34" s="41">
+        <v>263995.67436681729</v>
+      </c>
     </row>
     <row r="35" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
@@ -1367,6 +1787,12 @@
       <c r="G35" s="15">
         <v>9339929.5945354141</v>
       </c>
+      <c r="M35" s="42">
+        <v>2002</v>
+      </c>
+      <c r="N35" s="41">
+        <v>235234.59675290697</v>
+      </c>
     </row>
     <row r="36" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
@@ -1388,6 +1814,12 @@
       <c r="G36" s="19">
         <v>10874929.097083896</v>
       </c>
+      <c r="M36" s="42">
+        <v>2003</v>
+      </c>
+      <c r="N36" s="41">
+        <v>256022.46524751041</v>
+      </c>
     </row>
     <row r="37" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
@@ -1408,6 +1840,12 @@
       </c>
       <c r="G37" s="19">
         <v>11380763.411127962</v>
+      </c>
+      <c r="M37" s="42">
+        <v>2004</v>
+      </c>
+      <c r="N37" s="41">
+        <v>279020</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
@@ -1562,8 +2000,6 @@
       <c r="J44" s="17"/>
       <c r="K44" s="17"/>
       <c r="L44" s="17"/>
-      <c r="M44" s="17"/>
-      <c r="N44" s="17"/>
       <c r="O44" s="17"/>
       <c r="P44" s="17"/>
       <c r="Q44" s="17"/>
@@ -1605,6 +2041,8 @@
       <c r="G45" s="19">
         <v>14211513.62051825</v>
       </c>
+      <c r="M45" s="17"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
@@ -1819,6 +2257,9 @@
       <c r="O65" s="17"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="I10:J10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>

--- a/Serie PBG.xlsx
+++ b/Serie PBG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Facultad\Proyecto-evolucion-salarios\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C025D463-802B-4327-AD1A-CD0D5F2B98EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8667CD76-D979-417E-8F64-F436F7DDA565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="11">
   <si>
     <t>Año</t>
   </si>
@@ -98,16 +98,13 @@
     <t>Miles de pesos de 1993</t>
   </si>
   <si>
-    <t>Tasa de conversion 1 peso=0,0001 austral</t>
+    <t>PBI a precios de mercadoBase Ferreres (mill. de $ 1993)</t>
   </si>
   <si>
-    <t>PBG convertido</t>
+    <t>Variación del IPC</t>
   </si>
   <si>
-    <t>Prueba de como poner la variación entre cambios de monedas</t>
-  </si>
-  <si>
-    <t>PBI a precios de mercadoBase Ferreres (mill. de $ 1993)</t>
+    <t>Variación del PBI</t>
   </si>
 </sst>
 </file>
@@ -123,7 +120,7 @@
     <numFmt numFmtId="169" formatCode="#,##0\ \ \ \ "/>
     <numFmt numFmtId="170" formatCode="#,##0\ \ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,12 +162,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="6"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -208,7 +199,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -258,99 +249,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -363,9 +261,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="14"/>
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -384,13 +282,7 @@
     <xf numFmtId="4" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -408,9 +300,6 @@
     <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="3" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -420,54 +309,18 @@
     <xf numFmtId="3" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -690,7 +543,7 @@
   <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="14.42578125" style="22"/>
+    <col min="7" max="7" width="14.42578125" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -709,17 +562,17 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" s="21" t="s">
+      <c r="F1" s="21" t="s">
         <v>9</v>
       </c>
       <c r="M1" t="s">
         <v>0</v>
       </c>
       <c r="N1" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="O1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -738,17 +591,10 @@
       <c r="E2" s="5">
         <v>4.7536083333333332E-10</v>
       </c>
-      <c r="F2">
-        <v>1E-4</v>
-      </c>
-      <c r="G2" s="22">
-        <f>B2/$F$2</f>
-        <v>3134300</v>
-      </c>
-      <c r="M2" s="42">
+      <c r="M2" s="19">
         <v>1969</v>
       </c>
-      <c r="N2" s="41">
+      <c r="N2" s="18">
         <v>152643.77335610622</v>
       </c>
     </row>
@@ -769,15 +615,19 @@
       <c r="E3" s="5">
         <v>6.4042000000000005E-10</v>
       </c>
-      <c r="G3" s="22">
-        <f>B3/$F$2</f>
-        <v>3344100</v>
-      </c>
-      <c r="M3" s="43">
+      <c r="F3" s="22">
+        <f>E3/E2</f>
+        <v>1.3472292100912817</v>
+      </c>
+      <c r="M3" s="20">
         <v>1970</v>
       </c>
-      <c r="N3" s="41">
+      <c r="N3" s="18">
         <v>160860.95636173122</v>
+      </c>
+      <c r="O3">
+        <f>N3/N2</f>
+        <v>1.0538324153351146</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -797,15 +647,19 @@
       <c r="E4" s="5">
         <v>1.0147766666666666E-9</v>
       </c>
-      <c r="G4" s="22">
-        <f t="shared" ref="G4:G17" si="1">B4/$F$2</f>
-        <v>3562599.9999999995</v>
-      </c>
-      <c r="M4" s="42">
+      <c r="F4" s="22">
+        <f t="shared" ref="F4:F54" si="1">E4/E3</f>
+        <v>1.5845486815943701</v>
+      </c>
+      <c r="M4" s="19">
         <v>1971</v>
       </c>
-      <c r="N4" s="41">
+      <c r="N4" s="18">
         <v>166912.60622155317</v>
+      </c>
+      <c r="O4">
+        <f>N4/N3</f>
+        <v>1.0376203772294719</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -825,26 +679,23 @@
       <c r="E5" s="5">
         <v>1.6267208333333335E-9</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="22">
-        <f t="shared" si="1"/>
-        <v>3643299.9999999995</v>
-      </c>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="8"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="42">
+      <c r="F5" s="22">
+        <f t="shared" si="1"/>
+        <v>1.6030333439541709</v>
+      </c>
+      <c r="M5" s="19">
         <v>1972</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="18">
         <v>170379.33445085437</v>
       </c>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
+      <c r="O5">
+        <f t="shared" ref="O5:O37" si="2">N5/N4</f>
+        <v>1.0207697208004745</v>
+      </c>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
     </row>
     <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
@@ -863,15 +714,19 @@
       <c r="E6" s="5">
         <v>2.0206541666666667E-9</v>
       </c>
-      <c r="G6" s="22">
-        <f t="shared" si="1"/>
-        <v>4063700</v>
-      </c>
-      <c r="M6" s="42">
+      <c r="F6" s="22">
+        <f t="shared" si="1"/>
+        <v>1.2421640672825955</v>
+      </c>
+      <c r="M6" s="19">
         <v>1973</v>
       </c>
-      <c r="N6" s="41">
+      <c r="N6" s="18">
         <v>176760.97430606186</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="2"/>
+        <v>1.0374554805943808</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -891,23 +746,20 @@
       <c r="E7" s="5">
         <v>5.7142666666666667E-9</v>
       </c>
-      <c r="F7" s="10"/>
-      <c r="G7" s="22">
-        <f t="shared" si="1"/>
-        <v>3551999.9999999995</v>
-      </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="42">
+      <c r="F7" s="22">
+        <f t="shared" si="1"/>
+        <v>2.8279290741240977</v>
+      </c>
+      <c r="M7" s="19">
         <v>1974</v>
       </c>
-      <c r="N7" s="41">
+      <c r="N7" s="18">
         <v>186316.01795022786</v>
       </c>
-      <c r="O7" s="10"/>
+      <c r="O7">
+        <f t="shared" si="2"/>
+        <v>1.0540562965421396</v>
+      </c>
     </row>
     <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
@@ -926,15 +778,19 @@
       <c r="E8" s="5">
         <v>3.1086300000000001E-8</v>
       </c>
-      <c r="G8" s="22">
-        <f t="shared" si="1"/>
-        <v>4040500</v>
-      </c>
-      <c r="M8" s="42">
+      <c r="F8" s="22">
+        <f t="shared" si="1"/>
+        <v>5.4401206337354457</v>
+      </c>
+      <c r="M8" s="19">
         <v>1975</v>
       </c>
-      <c r="N8" s="41">
+      <c r="N8" s="18">
         <v>185210.55146568603</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="2"/>
+        <v>0.99406671258486679</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -954,22 +810,26 @@
       <c r="E9" s="5">
         <v>8.5808049999999979E-8</v>
       </c>
-      <c r="G9" s="22">
-        <f t="shared" si="1"/>
-        <v>3806300</v>
-      </c>
-      <c r="M9" s="42">
+      <c r="F9" s="22">
+        <f t="shared" si="1"/>
+        <v>2.7603172458607159</v>
+      </c>
+      <c r="M9" s="19">
         <v>1976</v>
       </c>
-      <c r="N9" s="41">
+      <c r="N9" s="18">
         <v>185188.55213266029</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="2"/>
+        <v>0.99988121987191525</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>1978</v>
       </c>
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>423.6</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -982,26 +842,26 @@
       <c r="E10" s="5">
         <v>2.3640874999999998E-7</v>
       </c>
-      <c r="G10" s="22">
-        <f t="shared" si="1"/>
-        <v>4236000</v>
-      </c>
-      <c r="I10" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10" s="40"/>
-      <c r="M10" s="42">
+      <c r="F10" s="22">
+        <f t="shared" si="1"/>
+        <v>2.7550882463824786</v>
+      </c>
+      <c r="M10" s="19">
         <v>1977</v>
       </c>
-      <c r="N10" s="41">
+      <c r="N10" s="18">
         <v>197015.02691173065</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="2"/>
+        <v>1.063861802702569</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>1979</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="9">
         <v>481.05</v>
       </c>
       <c r="C11" s="3" t="s">
@@ -1014,26 +874,26 @@
       <c r="E11" s="5">
         <v>6.1350683333333345E-7</v>
       </c>
-      <c r="G11" s="23">
-        <f t="shared" si="1"/>
-        <v>4810500</v>
-      </c>
-      <c r="H11" s="26"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="28"/>
-      <c r="M11" s="42">
+      <c r="F11" s="22">
+        <f t="shared" si="1"/>
+        <v>2.5951105165664701</v>
+      </c>
+      <c r="M11" s="19">
         <v>1978</v>
       </c>
-      <c r="N11" s="41">
+      <c r="N11" s="18">
         <v>190666.38605606163</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="2"/>
+        <v>0.96777585468892469</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>1980</v>
       </c>
-      <c r="B12" s="11">
+      <c r="B12" s="9">
         <v>429.24</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -1046,26 +906,26 @@
       <c r="E12" s="5">
         <v>1.2317019999999998E-6</v>
       </c>
-      <c r="G12" s="23">
-        <f t="shared" si="1"/>
-        <v>4292400</v>
-      </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="J12" s="30"/>
-      <c r="K12" s="31"/>
-      <c r="M12" s="42">
+      <c r="F12" s="22">
+        <f t="shared" si="1"/>
+        <v>2.0076418600064487</v>
+      </c>
+      <c r="M12" s="19">
         <v>1979</v>
       </c>
-      <c r="N12" s="41">
+      <c r="N12" s="18">
         <v>203891.65176001663</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="2"/>
+        <v>1.0693633837485459</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>1981</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="9">
         <v>351.83</v>
       </c>
       <c r="C13" s="3" t="s">
@@ -1078,32 +938,26 @@
       <c r="E13" s="5">
         <v>2.5185499999999998E-6</v>
       </c>
-      <c r="G13" s="23">
-        <f t="shared" si="1"/>
-        <v>3518299.9999999995</v>
-      </c>
-      <c r="H13" s="29"/>
-      <c r="I13" s="32">
-        <v>6485507</v>
-      </c>
-      <c r="J13" s="32">
-        <v>7035026</v>
-      </c>
-      <c r="K13" s="33">
-        <v>7761508</v>
-      </c>
-      <c r="M13" s="43">
+      <c r="F13" s="22">
+        <f>E13/E12</f>
+        <v>2.0447721932740226</v>
+      </c>
+      <c r="M13" s="20">
         <v>1980</v>
       </c>
-      <c r="N13" s="41">
+      <c r="N13" s="18">
         <v>207011.43217472488</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="2"/>
+        <v>1.0153011679869084</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>1982</v>
       </c>
-      <c r="B14" s="11">
+      <c r="B14" s="9">
         <v>360.43</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -1116,35 +970,26 @@
       <c r="E14" s="5">
         <v>6.6685833333333333E-6</v>
       </c>
-      <c r="G14" s="23">
-        <f t="shared" si="1"/>
-        <v>3604300</v>
-      </c>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30">
-        <f>I13/I15</f>
-        <v>24.984713709506547</v>
-      </c>
-      <c r="J14" s="30">
-        <f t="shared" ref="J14:K14" si="2">J13/J15</f>
-        <v>25.354277414774263</v>
-      </c>
-      <c r="K14" s="31">
-        <f t="shared" si="2"/>
-        <v>26.13610358123011</v>
-      </c>
-      <c r="M14" s="42">
+      <c r="F14" s="22">
+        <f t="shared" si="1"/>
+        <v>2.6477867556067314</v>
+      </c>
+      <c r="M14" s="19">
         <v>1981</v>
       </c>
-      <c r="N14" s="41">
+      <c r="N14" s="18">
         <v>195787.08557126726</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="2"/>
+        <v>0.94577909787134906</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>1983</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="9">
         <v>419.26</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -1157,32 +1002,26 @@
       <c r="E15" s="5">
         <v>2.9595141666666666E-5</v>
       </c>
-      <c r="G15" s="23">
-        <f t="shared" si="1"/>
-        <v>4192599.9999999995</v>
-      </c>
-      <c r="H15" s="29"/>
-      <c r="I15" s="34">
-        <v>259579</v>
-      </c>
-      <c r="J15" s="34">
-        <v>277469</v>
-      </c>
-      <c r="K15" s="35">
-        <v>296965</v>
-      </c>
-      <c r="M15" s="42">
+      <c r="F15" s="22">
+        <f t="shared" si="1"/>
+        <v>4.4379953263436764</v>
+      </c>
+      <c r="M15" s="19">
         <v>1982</v>
       </c>
-      <c r="N15" s="41">
+      <c r="N15" s="18">
         <v>189602.24152446413</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="2"/>
+        <v>0.96841035746174475</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>1984</v>
       </c>
-      <c r="B16" s="11">
+      <c r="B16" s="9">
         <v>404.44</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -1195,26 +1034,26 @@
       <c r="E16" s="5">
         <v>2.1507783333333334E-4</v>
       </c>
-      <c r="G16" s="23">
-        <f t="shared" si="1"/>
-        <v>4044400</v>
-      </c>
-      <c r="H16" s="29"/>
-      <c r="I16" s="30"/>
-      <c r="J16" s="30"/>
-      <c r="K16" s="31"/>
-      <c r="M16" s="42">
+      <c r="F16" s="22">
+        <f t="shared" si="1"/>
+        <v>7.2673358267981492</v>
+      </c>
+      <c r="M16" s="19">
         <v>1983</v>
       </c>
-      <c r="N16" s="41">
+      <c r="N16" s="18">
         <v>197400.61051265232</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="2"/>
+        <v>1.0411301518668068</v>
       </c>
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>1985</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="9">
         <v>384.61</v>
       </c>
       <c r="C17" s="3" t="s">
@@ -1227,29 +1066,26 @@
       <c r="E17" s="5">
         <v>1.6607925000000001E-3</v>
       </c>
-      <c r="G17" s="23">
-        <f t="shared" si="1"/>
-        <v>3846100</v>
-      </c>
-      <c r="H17" s="29"/>
-      <c r="I17" s="30">
-        <f>AVERAGE(I14:K14)</f>
-        <v>25.491698235170304</v>
-      </c>
-      <c r="J17" s="30"/>
-      <c r="K17" s="31"/>
-      <c r="M17" s="42">
+      <c r="F17" s="22">
+        <f t="shared" si="1"/>
+        <v>7.7218208602002223</v>
+      </c>
+      <c r="M17" s="19">
         <v>1984</v>
       </c>
-      <c r="N17" s="41">
+      <c r="N17" s="18">
         <v>201349.02459711238</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="2"/>
+        <v>1.0200020358306185</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>1986</v>
       </c>
-      <c r="B18" s="12">
+      <c r="B18" s="10">
         <v>267608.7</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -1262,28 +1098,26 @@
       <c r="E18" s="5">
         <v>3.1570041666666667E-3</v>
       </c>
-      <c r="G18" s="24">
-        <v>267608.7</v>
-      </c>
-      <c r="H18" s="29">
-        <f>G18*$I$17</f>
-        <v>6821800.22550622</v>
-      </c>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="31"/>
-      <c r="M18" s="42">
+      <c r="F18" s="22">
+        <f t="shared" si="1"/>
+        <v>1.9009022299093152</v>
+      </c>
+      <c r="M18" s="19">
         <v>1985</v>
       </c>
-      <c r="N18" s="41">
+      <c r="N18" s="18">
         <v>187351.74596487361</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="2"/>
+        <v>0.9304825108527518</v>
       </c>
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>1987</v>
       </c>
-      <c r="B19" s="12">
+      <c r="B19" s="10">
         <v>271052</v>
       </c>
       <c r="C19" s="3" t="s">
@@ -1296,28 +1130,26 @@
       <c r="E19" s="5">
         <v>7.3032416666666657E-3</v>
       </c>
-      <c r="G19" s="24">
-        <v>271052</v>
-      </c>
-      <c r="H19" s="29">
-        <f t="shared" ref="H19:H22" si="4">G19*$I$17</f>
-        <v>6909575.790039381</v>
-      </c>
-      <c r="I19" s="30"/>
-      <c r="J19" s="30"/>
-      <c r="K19" s="31"/>
-      <c r="M19" s="42">
+      <c r="F19" s="22">
+        <f t="shared" si="1"/>
+        <v>2.3133455900306328</v>
+      </c>
+      <c r="M19" s="19">
         <v>1986</v>
       </c>
-      <c r="N19" s="41">
+      <c r="N19" s="18">
         <v>200726.11957615431</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="2"/>
+        <v>1.071386437005974</v>
       </c>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
         <v>1988</v>
       </c>
-      <c r="B20" s="12">
+      <c r="B20" s="10">
         <v>264473</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -1327,31 +1159,29 @@
         <f t="shared" si="3"/>
         <v>121.27216266089812</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="11">
         <v>3.2350000000000004E-2</v>
       </c>
-      <c r="G20" s="24">
-        <v>264473</v>
-      </c>
-      <c r="H20" s="29">
-        <f t="shared" si="4"/>
-        <v>6741865.9073501956</v>
-      </c>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="31"/>
-      <c r="M20" s="42">
+      <c r="F20" s="22">
+        <f t="shared" si="1"/>
+        <v>4.4295398504545371</v>
+      </c>
+      <c r="M20" s="19">
         <v>1987</v>
       </c>
-      <c r="N20" s="41">
+      <c r="N20" s="18">
         <v>205926.37181563661</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="2"/>
+        <v>1.0259072025626907</v>
       </c>
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
         <v>1989</v>
       </c>
-      <c r="B21" s="12">
+      <c r="B21" s="10">
         <v>253410</v>
       </c>
       <c r="C21" s="3" t="s">
@@ -1361,31 +1191,29 @@
         <f t="shared" si="3"/>
         <v>116.19930480577673</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="11">
         <v>1.0285535833333335</v>
       </c>
-      <c r="G21" s="24">
-        <v>253410</v>
-      </c>
-      <c r="H21" s="29">
-        <f t="shared" si="4"/>
-        <v>6459851.2497745063</v>
-      </c>
-      <c r="I21" s="30"/>
-      <c r="J21" s="30"/>
-      <c r="K21" s="31"/>
-      <c r="M21" s="42">
+      <c r="F21" s="22">
+        <f t="shared" si="1"/>
+        <v>31.794546625450799</v>
+      </c>
+      <c r="M21" s="19">
         <v>1988</v>
       </c>
-      <c r="N21" s="41">
+      <c r="N21" s="18">
         <v>202022.16389395422</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="2"/>
+        <v>0.9810407579793724</v>
       </c>
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
         <v>1990</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="10">
         <v>253627</v>
       </c>
       <c r="C22" s="3" t="s">
@@ -1395,31 +1223,29 @@
         <f t="shared" si="3"/>
         <v>116.29880857099063</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="12">
         <v>24.828900000000001</v>
       </c>
-      <c r="G22" s="24">
-        <v>253627</v>
-      </c>
-      <c r="H22" s="29">
-        <f t="shared" si="4"/>
-        <v>6465382.9482915383</v>
-      </c>
-      <c r="I22" s="30"/>
-      <c r="J22" s="30"/>
-      <c r="K22" s="31"/>
-      <c r="M22" s="42">
+      <c r="F22" s="22">
+        <f t="shared" si="1"/>
+        <v>24.139627144688539</v>
+      </c>
+      <c r="M22" s="19">
         <v>1989</v>
       </c>
-      <c r="N22" s="41">
+      <c r="N22" s="18">
         <v>188010.819664468</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="2"/>
+        <v>0.93064451959419126</v>
       </c>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
         <v>1991</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="13">
         <v>6485506.9469233276</v>
       </c>
       <c r="C23" s="3" t="s">
@@ -1429,837 +1255,863 @@
         <f>D22</f>
         <v>116.29880857099063</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E23" s="12">
         <v>67.453100000000006</v>
       </c>
-      <c r="F23" s="10"/>
-      <c r="G23" s="25">
-        <v>6485506.9469233276</v>
-      </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="31"/>
-      <c r="M23" s="43">
+      <c r="F23" s="22">
+        <f t="shared" si="1"/>
+        <v>2.7167172126030557</v>
+      </c>
+      <c r="M23" s="20">
         <v>1990</v>
       </c>
-      <c r="N23" s="41">
+      <c r="N23" s="18">
         <v>184568.76708091571</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="2"/>
+        <v>0.98169226329795745</v>
       </c>
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
         <v>1992</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="13">
         <v>7035025.5867938362</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D24" s="4">
-        <f t="shared" ref="D24:D54" si="5">$D$22*(B24/$B$23)</f>
+        <f t="shared" ref="D24:D54" si="4">$D$22*(B24/$B$23)</f>
         <v>126.15283596275975</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E24" s="12">
         <v>84.248900000000006</v>
       </c>
-      <c r="G24" s="25">
-        <v>7035025.5867938362</v>
-      </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="31"/>
-      <c r="M24" s="42">
+      <c r="F24" s="22">
+        <f t="shared" si="1"/>
+        <v>1.2489996753299699</v>
+      </c>
+      <c r="M24" s="19">
         <v>1991</v>
       </c>
-      <c r="N24" s="41">
+      <c r="N24" s="18">
         <v>204093.82543139864</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="2"/>
+        <v>1.1057874452936183</v>
       </c>
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
         <v>1993</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="13">
         <v>7761508.2247009035</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D25" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>139.18020081296368</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E25" s="12">
         <v>93.188999999999993</v>
       </c>
-      <c r="G25" s="25">
-        <v>7761508.2247009035</v>
-      </c>
-      <c r="H25" s="37"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="39"/>
-      <c r="M25" s="42">
+      <c r="F25" s="22">
+        <f t="shared" si="1"/>
+        <v>1.1061153320696173</v>
+      </c>
+      <c r="M25" s="19">
         <v>1992</v>
       </c>
-      <c r="N25" s="41">
+      <c r="N25" s="18">
         <v>223701.26799433088</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="2"/>
+        <v>1.0960707288497702</v>
       </c>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
         <v>1994</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="13">
         <v>8098028.310572112</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D26" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>145.21471521057683</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E26" s="12">
         <v>97.081800000000001</v>
       </c>
-      <c r="F26" s="16"/>
-      <c r="G26" s="15">
-        <v>8098028.310572112</v>
-      </c>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="42">
+      <c r="F26" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0417731706531888</v>
+      </c>
+      <c r="M26" s="19">
         <v>1993</v>
       </c>
-      <c r="N26" s="41">
+      <c r="N26" s="18">
         <v>236504.9802315725</v>
       </c>
-      <c r="O26" s="17"/>
-      <c r="P26" s="17"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-      <c r="S26" s="17"/>
-      <c r="T26" s="17"/>
-      <c r="U26" s="17"/>
-      <c r="V26" s="17"/>
-      <c r="W26" s="17"/>
+      <c r="O26">
+        <f t="shared" si="2"/>
+        <v>1.0572357606733194</v>
+      </c>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
         <v>1995</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <v>7908811.3856461942</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D27" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>141.82165694844821</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E27" s="12">
         <v>100.35939999999999</v>
       </c>
-      <c r="G27" s="15">
-        <v>7908811.3856461942</v>
-      </c>
-      <c r="M27" s="42">
+      <c r="F27" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0337612199196966</v>
+      </c>
+      <c r="M27" s="19">
         <v>1994</v>
       </c>
-      <c r="N27" s="41">
+      <c r="N27" s="18">
         <v>250307.88553631518</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="2"/>
+        <v>1.0583620069701181</v>
       </c>
     </row>
     <row r="28" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
         <v>1996</v>
       </c>
-      <c r="B28" s="15">
+      <c r="B28" s="13">
         <v>8135361.8772270568</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D28" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>145.88418474583582</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E28" s="12">
         <v>100.51560000000001</v>
       </c>
-      <c r="G28" s="15">
-        <v>8135361.8772270568</v>
-      </c>
-      <c r="M28" s="42">
+      <c r="F28" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0015564062758446</v>
+      </c>
+      <c r="M28" s="19">
         <v>1995</v>
       </c>
-      <c r="N28" s="41">
+      <c r="N28" s="18">
         <v>243186.10151946038</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="2"/>
+        <v>0.97154790388806367</v>
       </c>
     </row>
     <row r="29" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
         <v>1997</v>
       </c>
-      <c r="B29" s="15">
+      <c r="B29" s="13">
         <v>8905959.4449048098</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D29" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>159.70262326453033</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="12">
         <v>101.04689999999999</v>
       </c>
-      <c r="G29" s="15">
-        <v>8905959.4449048098</v>
-      </c>
-      <c r="M29" s="42">
+      <c r="F29" s="22">
+        <f t="shared" si="1"/>
+        <v>1.005285746690066</v>
+      </c>
+      <c r="M29" s="19">
         <v>1996</v>
       </c>
-      <c r="N29" s="41">
+      <c r="N29" s="18">
         <v>256626.24305584718</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="2"/>
+        <v>1.0552668982824716</v>
       </c>
     </row>
     <row r="30" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
         <v>1998</v>
       </c>
-      <c r="B30" s="15">
+      <c r="B30" s="13">
         <v>9488295.9322833791</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D30" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>170.14514382981497</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E30" s="12">
         <v>101.9813</v>
       </c>
-      <c r="G30" s="15">
-        <v>9488295.9322833791</v>
-      </c>
-      <c r="M30" s="42">
+      <c r="F30" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0092471911557901</v>
+      </c>
+      <c r="M30" s="19">
         <v>1997</v>
       </c>
-      <c r="N30" s="41">
+      <c r="N30" s="18">
         <v>277441.31762238021</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="2"/>
+        <v>1.0811104675760042</v>
       </c>
     </row>
     <row r="31" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A31" s="3">
         <v>1999</v>
       </c>
-      <c r="B31" s="15">
+      <c r="B31" s="13">
         <v>9252615.1693661101</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D31" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>165.91889102418298</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E31" s="12">
         <v>100.7915</v>
       </c>
-      <c r="G31" s="15">
-        <v>9252615.1693661101</v>
-      </c>
-      <c r="M31" s="42">
+      <c r="F31" s="22">
+        <f t="shared" si="1"/>
+        <v>0.98833315519609966</v>
+      </c>
+      <c r="M31" s="19">
         <v>1998</v>
       </c>
-      <c r="N31" s="41">
+      <c r="N31" s="18">
         <v>288122.8046077239</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="2"/>
+        <v>1.0384999865084337</v>
       </c>
     </row>
     <row r="32" spans="1:23" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A32" s="3">
         <v>2000</v>
       </c>
-      <c r="B32" s="15">
+      <c r="B32" s="13">
         <v>9002038.4513383135</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>161.42552234834085</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E32" s="12">
         <v>99.844899999999996</v>
       </c>
-      <c r="G32" s="15">
-        <v>9002038.4513383135</v>
-      </c>
-      <c r="M32" s="42">
+      <c r="F32" s="22">
+        <f t="shared" si="1"/>
+        <v>0.99060833502825141</v>
+      </c>
+      <c r="M32" s="19">
         <v>1999</v>
       </c>
-      <c r="N32" s="41">
+      <c r="N32" s="18">
         <v>278369.01387171785</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="2"/>
+        <v>0.96614710609496623</v>
       </c>
     </row>
     <row r="33" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
         <v>2001</v>
       </c>
-      <c r="B33" s="15">
+      <c r="B33" s="13">
         <v>8322993.4966704417</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D33" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>149.24881513943413</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="15">
         <v>98.781666666666652</v>
       </c>
-      <c r="G33" s="15">
-        <v>8322993.4966704417</v>
-      </c>
-      <c r="M33" s="43">
+      <c r="F33" s="22">
+        <f t="shared" si="1"/>
+        <v>0.98935115030078313</v>
+      </c>
+      <c r="M33" s="20">
         <v>2000</v>
       </c>
-      <c r="N33" s="41">
+      <c r="N33" s="18">
         <v>276172.18535265006</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="2"/>
+        <v>0.99210821460149956</v>
       </c>
     </row>
     <row r="34" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
         <v>2002</v>
       </c>
-      <c r="B34" s="15">
+      <c r="B34" s="13">
         <v>7772198.0394271128</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D34" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>139.37189172111891</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="15">
         <v>124.33499999999999</v>
       </c>
-      <c r="G34" s="15">
-        <v>7772198.0394271128</v>
-      </c>
-      <c r="M34" s="42">
+      <c r="F34" s="22">
+        <f t="shared" si="1"/>
+        <v>1.2586849786566334</v>
+      </c>
+      <c r="M34" s="19">
         <v>2001</v>
       </c>
-      <c r="N34" s="41">
+      <c r="N34" s="18">
         <v>263995.67436681729</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="2"/>
+        <v>0.95590971273850645</v>
       </c>
     </row>
     <row r="35" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
         <v>2003</v>
       </c>
-      <c r="B35" s="15">
+      <c r="B35" s="13">
         <v>9339929.5945354141</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D35" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>167.48462269348113</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="15">
         <v>141.05000000000001</v>
       </c>
-      <c r="G35" s="15">
-        <v>9339929.5945354141</v>
-      </c>
-      <c r="M35" s="42">
+      <c r="F35" s="22">
+        <f t="shared" si="1"/>
+        <v>1.13443519523867</v>
+      </c>
+      <c r="M35" s="19">
         <v>2002</v>
       </c>
-      <c r="N35" s="41">
+      <c r="N35" s="18">
         <v>235234.59675290697</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="2"/>
+        <v>0.89105473912444755</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
         <v>2004</v>
       </c>
-      <c r="B36" s="19">
+      <c r="B36" s="16">
         <v>10874929.097083896</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D36" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>195.01039897657333</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="15">
         <v>147.28</v>
       </c>
-      <c r="G36" s="19">
-        <v>10874929.097083896</v>
-      </c>
-      <c r="M36" s="42">
+      <c r="F36" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0441687344913151</v>
+      </c>
+      <c r="M36" s="19">
         <v>2003</v>
       </c>
-      <c r="N36" s="41">
+      <c r="N36" s="18">
         <v>256022.46524751041</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="2"/>
+        <v>1.0883707957143705</v>
       </c>
     </row>
     <row r="37" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
         <v>2005</v>
       </c>
-      <c r="B37" s="19">
+      <c r="B37" s="16">
         <v>11380763.411127962</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D37" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>204.08107433612355</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="15">
         <v>167.48</v>
       </c>
-      <c r="G37" s="19">
-        <v>11380763.411127962</v>
-      </c>
-      <c r="M37" s="42">
+      <c r="F37" s="22">
+        <f t="shared" si="1"/>
+        <v>1.1371537208039109</v>
+      </c>
+      <c r="M37" s="19">
         <v>2004</v>
       </c>
-      <c r="N37" s="41">
+      <c r="N37" s="18">
         <v>279020</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="2"/>
+        <v>1.0898262374368464</v>
       </c>
     </row>
     <row r="38" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
         <v>2006</v>
       </c>
-      <c r="B38" s="19">
+      <c r="B38" s="16">
         <v>12259303.976933869</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>219.83515831455196</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="15">
         <v>179.08</v>
       </c>
-      <c r="G38" s="19">
-        <v>12259303.976933869</v>
+      <c r="F38" s="22">
+        <f t="shared" si="1"/>
+        <v>1.069262001433007</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
         <v>2007</v>
       </c>
-      <c r="B39" s="19">
+      <c r="B39" s="16">
         <v>12770718.617713338</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D39" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>229.00590069370071</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="15">
         <v>194.89</v>
       </c>
-      <c r="G39" s="19">
-        <v>12770718.617713338</v>
+      <c r="F39" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0882845655572926</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
         <v>2008</v>
       </c>
-      <c r="B40" s="19">
+      <c r="B40" s="16">
         <v>13065173.97313641</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D40" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>234.28610581772668</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="15">
         <v>211.61661758333335</v>
       </c>
-      <c r="G40" s="19">
-        <v>13065173.97313641</v>
+      <c r="F40" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0858259407015924</v>
       </c>
     </row>
     <row r="41" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
         <v>2009</v>
       </c>
-      <c r="B41" s="19">
+      <c r="B41" s="16">
         <v>12700761.719855074</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D41" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>227.75142607223748</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="15">
         <v>224.88780650000001</v>
       </c>
-      <c r="G41" s="19">
-        <v>12700761.719855074</v>
+      <c r="F41" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0627133590368467</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
         <v>2010</v>
       </c>
-      <c r="B42" s="19">
+      <c r="B42" s="16">
         <v>13262431.723353179</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D42" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>237.82335302435985</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="15">
         <v>248.41401550000003</v>
       </c>
-      <c r="G42" s="19">
-        <v>13262431.723353179</v>
+      <c r="F42" s="22">
+        <f t="shared" si="1"/>
+        <v>1.1046130929290736</v>
       </c>
     </row>
     <row r="43" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
         <v>2011</v>
       </c>
-      <c r="B43" s="19">
+      <c r="B43" s="16">
         <v>13739583.703819767</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D43" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>246.37969369127993</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="15">
         <v>272.69744600000001</v>
       </c>
-      <c r="G43" s="19">
-        <v>13739583.703819767</v>
+      <c r="F43" s="22">
+        <f t="shared" si="1"/>
+        <v>1.0977538664681341</v>
       </c>
     </row>
     <row r="44" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
         <v>2012</v>
       </c>
-      <c r="B44" s="19">
+      <c r="B44" s="16">
         <v>13545085.639384663</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>242.89193346709314</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="15">
         <v>300.08478674999998</v>
       </c>
-      <c r="F44" s="16"/>
-      <c r="G44" s="19">
-        <v>13545085.639384663</v>
-      </c>
-      <c r="H44" s="17"/>
-      <c r="I44" s="17"/>
-      <c r="J44" s="17"/>
-      <c r="K44" s="17"/>
-      <c r="L44" s="17"/>
-      <c r="O44" s="17"/>
-      <c r="P44" s="17"/>
-      <c r="Q44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17">
-        <v>13585607.412423011</v>
-      </c>
-      <c r="U44" s="17">
-        <v>13410851.44597216</v>
-      </c>
-      <c r="V44" s="17">
-        <v>12342645.880973661</v>
-      </c>
-      <c r="W44" s="17">
-        <v>13635887.646933109</v>
-      </c>
-      <c r="X44" s="17">
-        <v>14178694.442281883</v>
-      </c>
+      <c r="F44" s="22">
+        <f t="shared" si="1"/>
+        <v>1.1004312330449915</v>
+      </c>
+      <c r="O44" s="14"/>
+      <c r="P44" s="14"/>
+      <c r="Q44" s="14"/>
+      <c r="R44" s="14"/>
+      <c r="S44" s="14"/>
+      <c r="T44" s="14"/>
+      <c r="U44" s="14"/>
+      <c r="V44" s="14"/>
+      <c r="W44" s="14"/>
+      <c r="X44" s="14"/>
     </row>
     <row r="45" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
         <v>2013</v>
       </c>
-      <c r="B45" s="19">
+      <c r="B45" s="16">
         <v>14211513.62051825</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D45" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>254.8423917486889</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="15">
         <v>331.95090075000002</v>
       </c>
-      <c r="G45" s="19">
-        <v>14211513.62051825</v>
-      </c>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17"/>
+      <c r="F45" s="22">
+        <f t="shared" si="1"/>
+        <v>1.1061903682126599</v>
+      </c>
+      <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
         <v>2014</v>
       </c>
-      <c r="B46" s="19">
+      <c r="B46" s="16">
         <v>13687924.078647634</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D46" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>245.4533277328573</v>
       </c>
       <c r="E46" s="4"/>
-      <c r="G46" s="19">
-        <v>13687924.078647634</v>
-      </c>
+      <c r="F46" s="22"/>
     </row>
     <row r="47" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>2015</v>
       </c>
-      <c r="B47" s="19">
+      <c r="B47" s="16">
         <v>14189502.676873595</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D47" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>254.44768913833843</v>
       </c>
       <c r="E47" s="4"/>
-      <c r="G47" s="19">
-        <v>14189502.676873595</v>
-      </c>
-      <c r="O47" s="17"/>
+      <c r="F47" s="22"/>
+      <c r="O47" s="14"/>
     </row>
     <row r="48" spans="1:24" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>2016</v>
       </c>
-      <c r="B48" s="19">
+      <c r="B48" s="16">
         <v>13373002.759948755</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D48" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>239.80612475273261</v>
       </c>
       <c r="E48" s="4"/>
-      <c r="G48" s="19">
-        <v>13373002.759948755</v>
-      </c>
-      <c r="O48" s="17"/>
+      <c r="F48" s="22"/>
+      <c r="O48" s="14"/>
     </row>
     <row r="49" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
         <v>2017</v>
       </c>
-      <c r="B49" s="19">
+      <c r="B49" s="16">
         <v>13655492.409271004</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D49" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>244.87175954715681</v>
       </c>
       <c r="E49" s="4"/>
-      <c r="G49" s="19">
-        <v>13655492.409271004</v>
-      </c>
-      <c r="O49" s="17"/>
+      <c r="F49" s="22"/>
+      <c r="O49" s="14"/>
     </row>
     <row r="50" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
         <v>2018</v>
       </c>
-      <c r="B50" s="19">
+      <c r="B50" s="16">
         <v>13585607.412423011</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D50" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>243.61857426234812</v>
       </c>
       <c r="E50" s="4"/>
-      <c r="G50" s="19">
-        <v>13585607.412423011</v>
-      </c>
-      <c r="O50" s="17"/>
+      <c r="F50" s="22"/>
+      <c r="O50" s="14"/>
     </row>
     <row r="51" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
         <v>2019</v>
       </c>
-      <c r="B51" s="19">
+      <c r="B51" s="16">
         <v>13410851.44597216</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D51" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>240.48483146394625</v>
       </c>
       <c r="E51" s="4"/>
-      <c r="G51" s="19">
-        <v>13410851.44597216</v>
-      </c>
-      <c r="O51" s="17"/>
+      <c r="F51" s="22"/>
+      <c r="O51" s="14"/>
     </row>
     <row r="52" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
         <v>2020</v>
       </c>
-      <c r="B52" s="19">
+      <c r="B52" s="16">
         <v>12342645.880973661</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D52" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>221.32965430741552</v>
       </c>
       <c r="E52" s="4"/>
-      <c r="G52" s="19">
-        <v>12342645.880973661</v>
-      </c>
-      <c r="O52" s="17"/>
+      <c r="F52" s="22"/>
+      <c r="O52" s="14"/>
     </row>
     <row r="53" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
         <v>2021</v>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="16">
         <v>13635887.646933109</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>244.52020483896297</v>
       </c>
       <c r="E53" s="4"/>
-      <c r="G53" s="19">
-        <v>13635887.646933109</v>
-      </c>
-      <c r="O53" s="17"/>
+      <c r="F53" s="22"/>
+      <c r="O53" s="14"/>
     </row>
     <row r="54" spans="1:15" ht="43.5" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
         <v>2022</v>
       </c>
-      <c r="B54" s="19">
+      <c r="B54" s="16">
         <v>14178694.442281883</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>254.25387471241018</v>
       </c>
       <c r="E54" s="4"/>
-      <c r="G54" s="19">
-        <v>14178694.442281883</v>
-      </c>
-      <c r="O54" s="17"/>
+      <c r="F54" s="22"/>
+      <c r="O54" s="14"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O55" s="17"/>
+      <c r="O55" s="14"/>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O56" s="17"/>
+      <c r="O56" s="14"/>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O57" s="17"/>
+      <c r="O57" s="14"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O58" s="17"/>
+      <c r="O58" s="14"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O59" s="17"/>
+      <c r="O59" s="14"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O60" s="17"/>
+      <c r="O60" s="14"/>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O61" s="17"/>
+      <c r="O61" s="14"/>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O62" s="17"/>
+      <c r="O62" s="14"/>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O63" s="17"/>
+      <c r="O63" s="14"/>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="O64" s="17"/>
+      <c r="O64" s="14"/>
     </row>
     <row r="65" spans="15:15" x14ac:dyDescent="0.25">
-      <c r="O65" s="17"/>
+      <c r="O65" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="I10:J10"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
